--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="26" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="171">
   <si>
     <t>!Table</t>
   </si>
@@ -44,34 +44,34 @@
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -87,138 +87,138 @@
       </rPr>
       <t>roupID</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Option</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!WeaponMastery</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>룬검</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>석궁</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>쌍권총</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>WeaponType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>RuneSword</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>CrossBow</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>DualPistols</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>TotalExperience</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MasteryLevelExp</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Level</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Item</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint_Achievement</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MaxPoint</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>업적 달성</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>레벨업시 획득</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillPoint</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!SkillPoint</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>BaseValue</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>PerLevelValue</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MaxLevel</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_DAMAGE_ADD</t>
   </si>
   <si>
     <t>OPT_ATK_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_ATK_SPEED_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_RATE_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Option</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -246,179 +246,175 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!EnumTable</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!bool</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>IsShared</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>지식의서 소모</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Skill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>NormalAttackSkill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
     <t>Melee</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Ranged</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>근거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>원거리</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>WeaponRangeType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!WeaponRangeType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>RangeType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!WeaponType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeaponMastery</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Skill_RuneSword_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Skill_CrossBow_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualPistols_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SourceType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillPointSourceType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MasteryLevel</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Item</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Achievement</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!SkillPointSourceType</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>마스터리 레벨업</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>스킬포인트 아이템</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>업적 달성</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AnimControllerName</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>DualBlades</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>쌍검</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualBlades_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Mastery_DualBlades</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Mastery_RuneSword</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Mastery_CrossBow</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Mastery_DualPistols</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AOC_Hero_CrossBow</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AOC_Hero_DualBlades</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AOC_Hero_DualPistols</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>AOC_Hero_RuneSword</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Dev_SkillIDs</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!Skill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -435,22 +431,22 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_MAX_HP_ADD</t>
   </si>
   <si>
     <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_ATK_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_DAMAGE_BONUS_ADD</t>
@@ -463,11 +459,11 @@
   </si>
   <si>
     <t>OPT_ATK_SPEED_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_CRIT_RATE_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
@@ -480,14 +476,14 @@
   </si>
   <si>
     <t>OPT_MAX_HP_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_HP_REGEN_ADD</t>
   </si>
   <si>
     <t>OPT_DEF_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>OPT_DAMAGE_REDUCTION_ADD</t>
@@ -503,63 +499,59 @@
   </si>
   <si>
     <t>OPT_MOVE_SPEED_ADD</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>TypeIcon_Weapon</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusOption</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusPerLevel</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MasteryLevelBonus</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusOption</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>LevelBonusPerLevel</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillTreeNodeGroupID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>NodePos_Column</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MaxRow</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>MaxColumn</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>skill_001</t>
@@ -617,31 +609,31 @@
   </si>
   <si>
     <t>PrevNodeID</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>일이삼사오육칠팔구십일이삼사오육</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>노드1</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>노드2</t>
@@ -696,27 +688,52 @@
   </si>
   <si>
     <t>NodePos_Row</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>SkillTreeNode</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>RequireTreePoint</t>
-    <phoneticPr fontId="10" type="noConversion"/>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Mastery_02</t>
+  </si>
+  <si>
+    <t>Icon_Mastery_03</t>
+  </si>
+  <si>
+    <t>Icon_Mastery_04</t>
+  </si>
+  <si>
+    <t>Icon_Mastery_01</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponMastery</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -952,100 +969,103 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1384,32 +1404,32 @@
         <v>51</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="22"/>
     </row>
     <row r="6" spans="1:3">
       <c r="B6" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="B7" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1441,7 +1461,7 @@
       <c r="C17" s="23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1472,8 +1492,8 @@
       <c r="A1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>60</v>
+      <c r="B1" s="33" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1485,7 +1505,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>18</v>
@@ -1494,28 +1514,28 @@
         <v>58</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
       <c r="K2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1527,7 +1547,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>59</v>
@@ -1536,7 +1556,7 @@
         <v>57</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>43</v>
@@ -1557,27 +1577,27 @@
         <v>2</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" t="s">
         <v>52</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" t="s">
         <v>40</v>
@@ -1586,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K4" s="8">
         <v>6</v>
@@ -1598,18 +1618,18 @@
         <v>101</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>19</v>
@@ -1618,7 +1638,7 @@
         <v>52</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
         <v>41</v>
@@ -1627,7 +1647,7 @@
         <v>1E-3</v>
       </c>
       <c r="J5" s="25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K5" s="8">
         <v>6</v>
@@ -1641,13 +1661,13 @@
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>20</v>
@@ -1656,7 +1676,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s">
         <v>42</v>
@@ -1665,7 +1685,7 @@
         <v>1E-3</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K6" s="8">
         <v>6</v>
@@ -1679,13 +1699,13 @@
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>21</v>
@@ -1694,7 +1714,7 @@
         <v>53</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s">
         <v>39</v>
@@ -1703,7 +1723,7 @@
         <v>0.02</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K7" s="8">
         <v>6</v>
@@ -1762,7 +1782,7 @@
       <c r="I22" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -1796,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="10"/>
@@ -1822,19 +1842,19 @@
         <v>7</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="K2" s="8" t="s">
         <v>13</v>
@@ -1865,7 +1885,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>9</v>
@@ -1900,13 +1920,13 @@
         <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G4" s="8">
         <v>1</v>
@@ -1917,7 +1937,7 @@
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L4" s="11">
         <v>2</v>
@@ -1937,13 +1957,13 @@
         <v>101</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G5" s="1">
         <v>1</v>
@@ -1952,7 +1972,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L5" s="1">
         <v>5</v>
@@ -1972,13 +1992,13 @@
         <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1987,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L6" s="1">
         <v>10</v>
@@ -2007,13 +2027,13 @@
         <v>101</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -2028,7 +2048,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L7" s="1">
         <v>10</v>
@@ -2049,13 +2069,13 @@
         <v>101</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
@@ -2067,7 +2087,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L8" s="11">
         <v>0.05</v>
@@ -2088,13 +2108,13 @@
         <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
@@ -2109,7 +2129,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L9" s="11">
         <v>0.1</v>
@@ -2129,13 +2149,13 @@
         <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -2167,13 +2187,13 @@
         <v>101</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G11" s="1">
         <v>3</v>
@@ -2188,7 +2208,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L11" s="1">
         <v>0.01</v>
@@ -2208,13 +2228,13 @@
         <v>101</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G12" s="1">
         <v>3</v>
@@ -2229,7 +2249,7 @@
         <v>15</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L12" s="1">
         <v>0.05</v>
@@ -2249,13 +2269,13 @@
         <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -2270,7 +2290,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L13" s="8">
         <v>5</v>
@@ -2290,13 +2310,13 @@
         <v>101</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G14" s="1">
         <v>4</v>
@@ -2308,7 +2328,7 @@
         <v>25</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L14" s="11">
         <v>50</v>
@@ -2328,13 +2348,13 @@
         <v>101</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -2346,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L15" s="11">
         <v>5</v>
@@ -2366,13 +2386,13 @@
         <v>101</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G16" s="1">
         <v>5</v>
@@ -2387,7 +2407,7 @@
         <v>40</v>
       </c>
       <c r="K16" s="25" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L16" s="11">
         <v>10</v>
@@ -2407,13 +2427,13 @@
         <v>101</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G17" s="1">
         <v>5</v>
@@ -2428,7 +2448,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L17" s="1">
         <v>0.02</v>
@@ -2448,13 +2468,13 @@
         <v>101</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -2469,7 +2489,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
@@ -2489,13 +2509,13 @@
         <v>101</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G19" s="1">
         <v>5</v>
@@ -2507,7 +2527,7 @@
         <v>40</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L19" s="8">
         <v>0.02</v>
@@ -2527,13 +2547,13 @@
         <v>101</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G20" s="1">
         <v>6</v>
@@ -2548,7 +2568,7 @@
         <v>55</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L20" s="11">
         <v>0.02</v>
@@ -2568,13 +2588,13 @@
         <v>101</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G21" s="8">
         <v>6</v>
@@ -2589,7 +2609,7 @@
         <v>55</v>
       </c>
       <c r="K21" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L21" s="11">
         <v>0.2</v>
@@ -2649,7 +2669,7 @@
       <c r="G33" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -2704,7 +2724,7 @@
         <v>47</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H2" s="8"/>
       <c r="J2" s="8"/>
@@ -2727,7 +2747,7 @@
         <v>46</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H3" s="8"/>
       <c r="J3" s="8"/>
@@ -2746,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4"/>
     </row>
@@ -2764,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5"/>
     </row>
@@ -2782,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G6"/>
     </row>
@@ -2937,7 +2957,7 @@
       <c r="I35" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5411,7 +5431,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -5431,10 +5451,10 @@
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1">
       <c r="A1" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="31" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5443,16 +5463,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5"/>
       <c r="B3" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>43</v>
@@ -5477,7 +5497,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -5533,7 +5553,7 @@
       <c r="D22" s="25"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -459,7 +459,7 @@
     <t>MasteryLevelBonus</t>
   </si>
   <si>
-    <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02;Skill_DualBlades_Passive_02</t>
+    <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -1080,7 +1080,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="149">
   <si>
     <t>!Enum</t>
   </si>
@@ -216,247 +216,258 @@
     <t>!Table</t>
   </si>
   <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>NodePos_Row</t>
+  </si>
+  <si>
+    <t>NodePos_Column</t>
+  </si>
+  <si>
+    <t>PrevNodeID</t>
+  </si>
+  <si>
+    <t>RequireTreePoint</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>BaseValue</t>
+  </si>
+  <si>
+    <t>PerLevelValue</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육</t>
+  </si>
+  <si>
+    <t>skill_001</t>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+  </si>
+  <si>
+    <t>skill_002</t>
+  </si>
+  <si>
+    <t>OPT_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>노드3</t>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+  </si>
+  <si>
+    <t>skill_003</t>
+  </si>
+  <si>
+    <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>노드4</t>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+  </si>
+  <si>
+    <t>skill_004</t>
+  </si>
+  <si>
+    <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>노드5</t>
+  </si>
+  <si>
+    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
+  </si>
+  <si>
+    <t>skill_005</t>
+  </si>
+  <si>
+    <t>노드6</t>
+  </si>
+  <si>
+    <t>skill_006</t>
+  </si>
+  <si>
+    <t>노드7</t>
+  </si>
+  <si>
+    <t>skill_007</t>
+  </si>
+  <si>
+    <t>노드8</t>
+  </si>
+  <si>
+    <t>skill_008</t>
+  </si>
+  <si>
+    <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
+  </si>
+  <si>
+    <t>노드9</t>
+  </si>
+  <si>
+    <t>skill_009</t>
+  </si>
+  <si>
+    <t>OPT_BOSS_DAMAGE_BONUS_ADD</t>
+  </si>
+  <si>
+    <t>노드10</t>
+  </si>
+  <si>
+    <t>skill_010</t>
+  </si>
+  <si>
+    <t>OPT_DEF_PEN_ADD</t>
+  </si>
+  <si>
+    <t>노드11</t>
+  </si>
+  <si>
+    <t>skill_011</t>
+  </si>
+  <si>
+    <t>OPT_MAX_HP_ADD</t>
+  </si>
+  <si>
+    <t>노드12</t>
+  </si>
+  <si>
+    <t>skill_012</t>
+  </si>
+  <si>
+    <t>OPT_HP_REGEN_ADD</t>
+  </si>
+  <si>
+    <t>노드13</t>
+  </si>
+  <si>
+    <t>skill_013</t>
+  </si>
+  <si>
+    <t>OPT_DEF_ADD</t>
+  </si>
+  <si>
+    <t>노드14</t>
+  </si>
+  <si>
+    <t>skill_014</t>
+  </si>
+  <si>
+    <t>OPT_DAMAGE_REDUCTION_ADD</t>
+  </si>
+  <si>
+    <t>노드15</t>
+  </si>
+  <si>
+    <t>skill_015</t>
+  </si>
+  <si>
+    <t>OPT_LIFE_ON_HIT_ADD</t>
+  </si>
+  <si>
+    <t>노드16</t>
+  </si>
+  <si>
+    <t>skill_016</t>
+  </si>
+  <si>
+    <t>OPT_EVASION_RATE_ADD</t>
+  </si>
+  <si>
+    <t>노드17</t>
+  </si>
+  <si>
+    <t>skill_017</t>
+  </si>
+  <si>
+    <t>OPT_BLOCK_RATE_ADD</t>
+  </si>
+  <si>
+    <t>노드18</t>
+  </si>
+  <si>
+    <t>skill_018</t>
+  </si>
+  <si>
+    <t>OPT_MOVE_SPEED_ADD</t>
+  </si>
+  <si>
+    <t>SkillPoint</t>
+  </si>
+  <si>
+    <t>MaxPoint</t>
+  </si>
+  <si>
+    <t>IsShared</t>
+  </si>
+  <si>
+    <t>SourceType</t>
+  </si>
+  <si>
+    <t>!SkillPoint</t>
+  </si>
+  <si>
+    <t>!bool</t>
+  </si>
+  <si>
+    <t>!SkillPointSourceType</t>
+  </si>
+  <si>
+    <t>SkillPoint_Level</t>
+  </si>
+  <si>
+    <t>레벨업시 획득</t>
+  </si>
+  <si>
+    <t>SkillPoint_Item</t>
+  </si>
+  <si>
+    <t>지식의서 소모</t>
+  </si>
+  <si>
+    <t>SkillPoint_Achievement</t>
+  </si>
+  <si>
+    <t>MasteryLevelExp</t>
+  </si>
+  <si>
+    <t>TotalExperience</t>
+  </si>
+  <si>
+    <t>MasteryLevelBonus</t>
+  </si>
+  <si>
+    <t>강타</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>찌르기</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반공격 5번마다 타겟을 강타하여 범위 데미지를 입힙니다.</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반공격 3번마다 직선으로 찌르기를 사용하여 데미지를 입힙니다.</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
     <t>SkillTreeNode</t>
-  </si>
-  <si>
-    <t>GroupID</t>
-  </si>
-  <si>
-    <t>Desc</t>
-  </si>
-  <si>
-    <t>NodePos_Row</t>
-  </si>
-  <si>
-    <t>NodePos_Column</t>
-  </si>
-  <si>
-    <t>PrevNodeID</t>
-  </si>
-  <si>
-    <t>RequireTreePoint</t>
-  </si>
-  <si>
-    <t>Option</t>
-  </si>
-  <si>
-    <t>BaseValue</t>
-  </si>
-  <si>
-    <t>PerLevelValue</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>노드1</t>
-  </si>
-  <si>
-    <t>일이삼사오육칠팔구십일이삼사오육</t>
-  </si>
-  <si>
-    <t>skill_001</t>
-  </si>
-  <si>
-    <t>노드2</t>
-  </si>
-  <si>
-    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-  </si>
-  <si>
-    <t>skill_002</t>
-  </si>
-  <si>
-    <t>OPT_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>노드3</t>
-  </si>
-  <si>
-    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-  </si>
-  <si>
-    <t>skill_003</t>
-  </si>
-  <si>
-    <t>OPT_MELEE_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>노드4</t>
-  </si>
-  <si>
-    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-  </si>
-  <si>
-    <t>skill_004</t>
-  </si>
-  <si>
-    <t>OPT_RANGE_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>노드5</t>
-  </si>
-  <si>
-    <t>일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육일이삼사오육칠팔구십일이삼사오육</t>
-  </si>
-  <si>
-    <t>skill_005</t>
-  </si>
-  <si>
-    <t>노드6</t>
-  </si>
-  <si>
-    <t>skill_006</t>
-  </si>
-  <si>
-    <t>노드7</t>
-  </si>
-  <si>
-    <t>skill_007</t>
-  </si>
-  <si>
-    <t>노드8</t>
-  </si>
-  <si>
-    <t>skill_008</t>
-  </si>
-  <si>
-    <t>OPT_FINAL_DAMAGE_AMP_ADD</t>
-  </si>
-  <si>
-    <t>노드9</t>
-  </si>
-  <si>
-    <t>skill_009</t>
-  </si>
-  <si>
-    <t>OPT_BOSS_DAMAGE_BONUS_ADD</t>
-  </si>
-  <si>
-    <t>노드10</t>
-  </si>
-  <si>
-    <t>skill_010</t>
-  </si>
-  <si>
-    <t>OPT_DEF_PEN_ADD</t>
-  </si>
-  <si>
-    <t>노드11</t>
-  </si>
-  <si>
-    <t>skill_011</t>
-  </si>
-  <si>
-    <t>OPT_MAX_HP_ADD</t>
-  </si>
-  <si>
-    <t>노드12</t>
-  </si>
-  <si>
-    <t>skill_012</t>
-  </si>
-  <si>
-    <t>OPT_HP_REGEN_ADD</t>
-  </si>
-  <si>
-    <t>노드13</t>
-  </si>
-  <si>
-    <t>skill_013</t>
-  </si>
-  <si>
-    <t>OPT_DEF_ADD</t>
-  </si>
-  <si>
-    <t>노드14</t>
-  </si>
-  <si>
-    <t>skill_014</t>
-  </si>
-  <si>
-    <t>OPT_DAMAGE_REDUCTION_ADD</t>
-  </si>
-  <si>
-    <t>노드15</t>
-  </si>
-  <si>
-    <t>skill_015</t>
-  </si>
-  <si>
-    <t>OPT_LIFE_ON_HIT_ADD</t>
-  </si>
-  <si>
-    <t>노드16</t>
-  </si>
-  <si>
-    <t>skill_016</t>
-  </si>
-  <si>
-    <t>OPT_EVASION_RATE_ADD</t>
-  </si>
-  <si>
-    <t>노드17</t>
-  </si>
-  <si>
-    <t>skill_017</t>
-  </si>
-  <si>
-    <t>OPT_BLOCK_RATE_ADD</t>
-  </si>
-  <si>
-    <t>노드18</t>
-  </si>
-  <si>
-    <t>skill_018</t>
-  </si>
-  <si>
-    <t>OPT_MOVE_SPEED_ADD</t>
-  </si>
-  <si>
-    <t>SkillPoint</t>
-  </si>
-  <si>
-    <t>MaxPoint</t>
-  </si>
-  <si>
-    <t>IsShared</t>
-  </si>
-  <si>
-    <t>SourceType</t>
-  </si>
-  <si>
-    <t>!SkillPoint</t>
-  </si>
-  <si>
-    <t>!bool</t>
-  </si>
-  <si>
-    <t>!SkillPointSourceType</t>
-  </si>
-  <si>
-    <t>SkillPoint_Level</t>
-  </si>
-  <si>
-    <t>레벨업시 획득</t>
-  </si>
-  <si>
-    <t>SkillPoint_Item</t>
-  </si>
-  <si>
-    <t>지식의서 소모</t>
-  </si>
-  <si>
-    <t>SkillPoint_Achievement</t>
-  </si>
-  <si>
-    <t>MasteryLevelExp</t>
-  </si>
-  <si>
-    <t>TotalExperience</t>
-  </si>
-  <si>
-    <t>MasteryLevelBonus</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
     <t>Skill_DualBlades_Active_01;Skill_DualBlades_Active_02</t>
@@ -1080,7 +1091,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1225,7 +1236,7 @@
       <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1350,8 +1361,8 @@
       <c r="M4" s="27">
         <v>101</v>
       </c>
-      <c r="N4" s="27" t="s">
-        <v>146</v>
+      <c r="N4" s="23" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1476,6 +1487,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="I13" s="23"/>
+      <c r="N13" s="23"/>
     </row>
     <row r="14" spans="1:14">
       <c r="I14" s="23"/>
@@ -1526,7 +1538,7 @@
     <col min="2" max="2" width="13.5" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.75" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.75" style="27" customWidth="1"/>
+    <col min="5" max="5" width="64.75" style="27" customWidth="1"/>
     <col min="6" max="6" width="18.75" style="27" customWidth="1"/>
     <col min="7" max="7" width="13.875" style="27" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.375" style="27" bestFit="1" customWidth="1"/>
@@ -1545,8 +1557,8 @@
       <c r="A1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>65</v>
+      <c r="B1" s="31" t="s">
+        <v>147</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="9"/>
@@ -1563,40 +1575,40 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" t="s">
         <v>73</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>75</v>
       </c>
       <c r="O2" s="8"/>
     </row>
@@ -1650,13 +1662,13 @@
         <v>101</v>
       </c>
       <c r="D4" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>76</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>78</v>
       </c>
       <c r="G4" s="7">
         <v>1</v>
@@ -1685,13 +1697,13 @@
         <v>101</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G5" s="27">
         <v>1</v>
@@ -1700,7 +1712,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="L5" s="27">
         <v>5</v>
@@ -1720,13 +1732,13 @@
         <v>101</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G6" s="27">
         <v>1</v>
@@ -1735,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="L6" s="27">
         <v>10</v>
@@ -1755,13 +1767,13 @@
         <v>101</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G7" s="27">
         <v>2</v>
@@ -1776,7 +1788,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L7" s="27">
         <v>10</v>
@@ -1797,13 +1809,13 @@
         <v>101</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G8" s="27">
         <v>2</v>
@@ -1835,13 +1847,13 @@
         <v>101</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G9" s="27">
         <v>2</v>
@@ -1876,13 +1888,13 @@
         <v>101</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G10" s="27">
         <v>3</v>
@@ -1914,13 +1926,13 @@
         <v>101</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G11" s="27">
         <v>3</v>
@@ -1935,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L11" s="27">
         <v>0.01</v>
@@ -1955,13 +1967,13 @@
         <v>101</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G12" s="27">
         <v>3</v>
@@ -1976,7 +1988,7 @@
         <v>15</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L12" s="27">
         <v>0.05</v>
@@ -1996,13 +2008,13 @@
         <v>101</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G13" s="27">
         <v>4</v>
@@ -2017,7 +2029,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L13" s="7">
         <v>5</v>
@@ -2037,13 +2049,13 @@
         <v>101</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="G14" s="27">
         <v>4</v>
@@ -2055,7 +2067,7 @@
         <v>25</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="L14" s="27">
         <v>50</v>
@@ -2075,13 +2087,13 @@
         <v>101</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G15" s="27">
         <v>4</v>
@@ -2093,7 +2105,7 @@
         <v>25</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L15" s="27">
         <v>5</v>
@@ -2113,13 +2125,13 @@
         <v>101</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G16" s="27">
         <v>5</v>
@@ -2134,7 +2146,7 @@
         <v>40</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L16" s="27">
         <v>10</v>
@@ -2154,13 +2166,13 @@
         <v>101</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G17" s="27">
         <v>5</v>
@@ -2175,7 +2187,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="L17" s="27">
         <v>0.02</v>
@@ -2195,13 +2207,13 @@
         <v>101</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="G18" s="27">
         <v>5</v>
@@ -2216,7 +2228,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L18" s="27">
         <v>5</v>
@@ -2236,13 +2248,13 @@
         <v>101</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G19" s="27">
         <v>5</v>
@@ -2254,7 +2266,7 @@
         <v>40</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L19" s="7">
         <v>0.02</v>
@@ -2274,13 +2286,13 @@
         <v>101</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G20" s="27">
         <v>6</v>
@@ -2295,7 +2307,7 @@
         <v>55</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="L20" s="27">
         <v>0.02</v>
@@ -2315,13 +2327,13 @@
         <v>101</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G21" s="7">
         <v>6</v>
@@ -2336,7 +2348,7 @@
         <v>55</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="L21" s="27">
         <v>0.2</v>
@@ -2408,7 +2420,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2423,16 +2435,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H2" s="7"/>
       <c r="J2" s="7"/>
@@ -2443,7 +2455,7 @@
     <row r="3" spans="1:13">
       <c r="A3" s="4"/>
       <c r="B3" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
         <v>35</v>
@@ -2452,23 +2464,23 @@
         <v>29</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H3" s="7"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E4" s="27" t="b">
         <v>0</v>
@@ -2479,13 +2491,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="B5" s="27" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E5" s="27" t="b">
         <v>0</v>
@@ -2496,7 +2508,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -2618,7 +2630,7 @@
         <v>64</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2627,7 +2639,7 @@
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
@@ -5085,7 +5097,7 @@
         <v>64</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5128,7 +5140,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D5">
         <v>5</v>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="5"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -1087,7 +1087,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="4"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -462,9 +462,6 @@
     <t>MasteryLevelExp</t>
   </si>
   <si>
-    <t>TotalExperience</t>
-  </si>
-  <si>
     <t>WeaponMastery</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -478,6 +475,10 @@
   </si>
   <si>
     <t>LevelBonusOption</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalExperience</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1087,7 +1088,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1233,7 +1234,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1257,7 +1258,7 @@
         <v>19</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I2" s="27" t="s">
         <v>20</v>
@@ -2662,7 +2663,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
@@ -5120,7 +5121,7 @@
         <v>62</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5129,7 +5130,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D2" s="27" t="s">
         <v>20</v>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -1088,7 +1088,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="3"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="9060" tabRatio="683" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -78,15 +78,9 @@
     <t>RangeType</t>
   </si>
   <si>
-    <t>AnimControllerName</t>
-  </si>
-  <si>
     <t>LevelBonusPerLevel</t>
   </si>
   <si>
-    <t>NormalAttackSkill</t>
-  </si>
-  <si>
     <t>MaxRow</t>
   </si>
   <si>
@@ -99,15 +93,9 @@
     <t>Dev_SkillIDs</t>
   </si>
   <si>
-    <t>!WeaponMastery</t>
-  </si>
-  <si>
     <t>!string</t>
   </si>
   <si>
-    <t>!WeaponType</t>
-  </si>
-  <si>
     <t>!WeaponRangeType</t>
   </si>
   <si>
@@ -123,90 +111,30 @@
     <t>!int</t>
   </si>
   <si>
-    <t>Mastery_DualBlades</t>
-  </si>
-  <si>
-    <t>쌍검</t>
-  </si>
-  <si>
     <t>Icon_Mastery_01</t>
   </si>
   <si>
-    <t>DualBlades</t>
-  </si>
-  <si>
-    <t>AOC_Hero_DualBlades</t>
-  </si>
-  <si>
     <t>OPT_ATK_ADD</t>
   </si>
   <si>
-    <t>Skill_DualBlades_Attack</t>
-  </si>
-  <si>
-    <t>Mastery_RuneSword</t>
-  </si>
-  <si>
-    <t>룬검</t>
-  </si>
-  <si>
     <t>Icon_Mastery_02</t>
   </si>
   <si>
-    <t>RuneSword</t>
-  </si>
-  <si>
-    <t>AOC_Hero_RuneSword</t>
-  </si>
-  <si>
     <t>OPT_ATK_SPEED_ADD</t>
   </si>
   <si>
-    <t>Skill_RuneSword_Attack</t>
-  </si>
-  <si>
-    <t>Mastery_CrossBow</t>
-  </si>
-  <si>
-    <t>석궁</t>
-  </si>
-  <si>
     <t>Icon_Mastery_03</t>
   </si>
   <si>
-    <t>CrossBow</t>
-  </si>
-  <si>
-    <t>AOC_Hero_CrossBow</t>
-  </si>
-  <si>
     <t>OPT_CRIT_RATE_ADD</t>
   </si>
   <si>
-    <t>Skill_CrossBow_Attack</t>
-  </si>
-  <si>
-    <t>Mastery_DualPistols</t>
-  </si>
-  <si>
-    <t>쌍권총</t>
-  </si>
-  <si>
     <t>Icon_Mastery_04</t>
   </si>
   <si>
-    <t>DualPistols</t>
-  </si>
-  <si>
-    <t>AOC_Hero_DualPistols</t>
-  </si>
-  <si>
     <t>OPT_CRIT_DAMAGE_ADD</t>
   </si>
   <si>
-    <t>Skill_DualPistols_Attack</t>
-  </si>
-  <si>
     <t>!Table</t>
   </si>
   <si>
@@ -252,21 +180,9 @@
     <t>PerLevelValue_02</t>
   </si>
   <si>
-    <t>쌍검 찌르기</t>
-  </si>
-  <si>
-    <t>쌍검찌르기를 습득한다. 레벨이 오를수록 피해량이 증가한다.</t>
-  </si>
-  <si>
     <t>skill_019</t>
   </si>
   <si>
-    <t>OPT_LEARN_DualBlades_Active_01</t>
-  </si>
-  <si>
-    <t>OPT_DMG_DualBlades_Active_01</t>
-  </si>
-  <si>
     <t>강타</t>
   </si>
   <si>
@@ -294,16 +210,7 @@
     <t>연속공격</t>
   </si>
   <si>
-    <t>쌍검찌르기가 발동하면 3초 동안 공격속도 10%가 증가한다. 최대 3중첩</t>
-  </si>
-  <si>
     <t>skill_004</t>
-  </si>
-  <si>
-    <t>OPT_APPEND_DualBlades_AtkSpeedBuff</t>
-  </si>
-  <si>
-    <t>OPT_ATKSPEED_DualBlades_Buff</t>
   </si>
   <si>
     <t>노드5</t>
@@ -479,6 +386,130 @@
   </si>
   <si>
     <t>TotalExperience</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>도</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>권총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>소총</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!WeaponMastery</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>!WeaponType</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimControllerName</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_GreatSword</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_Blade</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_Pistol</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOC_Hero_Rifle</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalAttackSkill</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_GreatSword</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreatSword</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_Blade</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Blade</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Blade_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_Pistol</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pistol</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Pistol_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_Rifle</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rifle</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_Rifle_Attack</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검 찌르기</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검찌르기를 습득한다. 레벨이 오를수록 피해량이 증가한다.</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_LEARN_GreatSword_Active_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_DMG_GreatSword_Active_01</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>대검찌르기가 발동하면 3초 동안 공격속도 10%가 증가한다. 최대 3중첩</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_APPEND_GreatSword_AtkSpeedBuff</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>OPT_ATKSPEED_GreatSword_Buff</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill_GreatSword_Attack_01</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1088,7 +1119,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1234,7 +1265,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1255,99 +1286,99 @@
         <v>18</v>
       </c>
       <c r="G2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="K2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="L2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="N2" s="27" t="s">
         <v>23</v>
-      </c>
-      <c r="M2" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="27" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="I3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="J3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="K3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="27" t="s">
-        <v>33</v>
-      </c>
       <c r="L3" s="27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M3" s="27" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="N3" s="27" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="B4" s="27" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="K4" s="7">
         <v>6</v>
@@ -1362,31 +1393,31 @@
     </row>
     <row r="5" spans="1:14">
       <c r="B5" s="27" t="s">
-        <v>41</v>
+        <v>135</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I5">
         <v>1E-3</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="K5" s="7">
         <v>6</v>
@@ -1400,31 +1431,31 @@
     </row>
     <row r="6" spans="1:14">
       <c r="B6" s="27" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G6" s="26" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="I6">
         <v>1E-3</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="K6" s="7">
         <v>6</v>
@@ -1438,31 +1469,31 @@
     </row>
     <row r="7" spans="1:14">
       <c r="B7" s="27" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I7">
         <v>0.02</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="K7" s="7">
         <v>6</v>
@@ -1549,10 +1580,10 @@
   <sheetData>
     <row r="1" spans="1:17" s="3" customFormat="1">
       <c r="A1" s="6" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="9"/>
@@ -1569,100 +1600,100 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="I2" s="27" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="M2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="Q2" s="7" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="N3" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="Q3" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -1673,13 +1704,13 @@
         <v>101</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="G4" s="7">
         <v>1</v>
@@ -1688,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="L4" s="27">
         <v>0</v>
@@ -1700,7 +1731,7 @@
         <v>5</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="P4" s="27">
         <v>0</v>
@@ -1717,13 +1748,13 @@
         <v>101</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E5" s="27" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="G5" s="27">
         <v>1</v>
@@ -1732,7 +1763,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="L5" s="27">
         <v>5</v>
@@ -1752,13 +1783,13 @@
         <v>101</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="G6" s="27">
         <v>1</v>
@@ -1767,7 +1798,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="L6" s="27">
         <v>10</v>
@@ -1787,13 +1818,13 @@
         <v>101</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="G7" s="27">
         <v>2</v>
@@ -1808,7 +1839,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1820,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="P7">
         <v>0.1</v>
@@ -1837,13 +1868,13 @@
         <v>101</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="G8" s="27">
         <v>2</v>
@@ -1855,7 +1886,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="L8" s="27">
         <v>0.05</v>
@@ -1875,13 +1906,13 @@
         <v>101</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="G9" s="27">
         <v>2</v>
@@ -1896,7 +1927,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="L9" s="27">
         <v>0.1</v>
@@ -1916,13 +1947,13 @@
         <v>101</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="G10" s="27">
         <v>3</v>
@@ -1934,7 +1965,7 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="L10" s="27">
         <v>0.2</v>
@@ -1954,13 +1985,13 @@
         <v>101</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G11" s="27">
         <v>3</v>
@@ -1975,7 +2006,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="L11" s="27">
         <v>0.01</v>
@@ -1995,13 +2026,13 @@
         <v>101</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G12" s="27">
         <v>3</v>
@@ -2016,7 +2047,7 @@
         <v>15</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="L12" s="27">
         <v>0.05</v>
@@ -2036,13 +2067,13 @@
         <v>101</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="G13" s="27">
         <v>4</v>
@@ -2057,7 +2088,7 @@
         <v>25</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="L13" s="7">
         <v>5</v>
@@ -2077,13 +2108,13 @@
         <v>101</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="G14" s="27">
         <v>4</v>
@@ -2095,7 +2126,7 @@
         <v>25</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="L14" s="27">
         <v>50</v>
@@ -2115,13 +2146,13 @@
         <v>101</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F15" s="27" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="G15" s="27">
         <v>4</v>
@@ -2133,7 +2164,7 @@
         <v>25</v>
       </c>
       <c r="K15" s="23" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="L15" s="27">
         <v>5</v>
@@ -2153,13 +2184,13 @@
         <v>101</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="G16" s="27">
         <v>5</v>
@@ -2174,7 +2205,7 @@
         <v>40</v>
       </c>
       <c r="K16" s="23" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="L16" s="27">
         <v>10</v>
@@ -2194,13 +2225,13 @@
         <v>101</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="G17" s="27">
         <v>5</v>
@@ -2215,7 +2246,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="L17" s="27">
         <v>0.02</v>
@@ -2235,13 +2266,13 @@
         <v>101</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F18" s="27" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="G18" s="27">
         <v>5</v>
@@ -2256,7 +2287,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="23" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="L18" s="27">
         <v>5</v>
@@ -2276,13 +2307,13 @@
         <v>101</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="G19" s="27">
         <v>5</v>
@@ -2294,7 +2325,7 @@
         <v>40</v>
       </c>
       <c r="K19" s="23" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="L19" s="7">
         <v>0.02</v>
@@ -2314,13 +2345,13 @@
         <v>101</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G20" s="27">
         <v>6</v>
@@ -2335,7 +2366,7 @@
         <v>55</v>
       </c>
       <c r="K20" s="23" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="L20" s="27">
         <v>0.02</v>
@@ -2355,13 +2386,13 @@
         <v>101</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="G21" s="7">
         <v>6</v>
@@ -2376,7 +2407,7 @@
         <v>55</v>
       </c>
       <c r="K21" s="23" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L21" s="27">
         <v>0.2</v>
@@ -2444,7 +2475,7 @@
         <v>13</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -2459,16 +2490,16 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="H2" s="7"/>
       <c r="J2" s="7"/>
@@ -2479,32 +2510,32 @@
     <row r="3" spans="1:13">
       <c r="A3" s="4"/>
       <c r="B3" s="12" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E3" s="27" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="H3" s="7"/>
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:13">
       <c r="B4" s="27" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="E4" s="27" t="b">
         <v>0</v>
@@ -2515,13 +2546,13 @@
     </row>
     <row r="5" spans="1:13">
       <c r="B5" s="27" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="C5">
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="E5" s="27" t="b">
         <v>0</v>
@@ -2532,7 +2563,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="27" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -2651,10 +2682,10 @@
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1">
       <c r="A1" s="6" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -2663,7 +2694,7 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="D2" s="14"/>
       <c r="E2" s="14"/>
@@ -2672,10 +2703,10 @@
     <row r="3" spans="1:10">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D3" s="14"/>
       <c r="E3" s="14"/>
@@ -5118,10 +5149,10 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1">
       <c r="A1" s="28" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5130,22 +5161,22 @@
         <v>14</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5153,7 +5184,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>2.5</v>
@@ -5164,7 +5195,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>5</v>

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="142">
   <si>
     <t>!Enum</t>
   </si>
@@ -413,30 +413,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>AnimControllerName</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_GreatSword</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_Blade</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_Pistol</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOC_Hero_Rifle</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>NormalAttackSkill</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Mastery_GreatSword</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -453,10 +429,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Blade_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Mastery_Pistol</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -465,10 +437,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Pistol_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Mastery_Rifle</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -477,10 +445,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Skill_Rifle_Attack</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>대검 찌르기</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -506,10 +470,6 @@
   </si>
   <si>
     <t>OPT_ATKSPEED_GreatSword_Buff</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill_GreatSword_Attack_01</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -759,7 +719,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
@@ -831,9 +791,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1133,12 +1090,12 @@
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.875" style="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="45.625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.125" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="34.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.125" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="9" style="27" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="27"/>
+    <col min="4" max="4" width="21.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="9" style="26" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="15" customFormat="1">
@@ -1213,22 +1170,22 @@
       <c r="C11" s="21"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="C12" s="27"/>
+      <c r="C12" s="26"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="C13" s="27"/>
+      <c r="C13" s="26"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="C14" s="27"/>
+      <c r="C14" s="26"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="C15" s="27"/>
+      <c r="C15" s="26"/>
     </row>
     <row r="16" spans="1:3">
       <c r="C16" s="21"/>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="27"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="21"/>
     </row>
   </sheetData>
@@ -1239,36 +1196,34 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.75" style="27" customWidth="1"/>
-    <col min="7" max="7" width="21.875" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.125" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.25" style="27" customWidth="1"/>
-    <col min="14" max="14" width="25.375" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="9" style="27" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="27"/>
+    <col min="2" max="2" width="19.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" style="26" customWidth="1"/>
+    <col min="7" max="7" width="24.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.25" style="26" customWidth="1"/>
+    <col min="12" max="12" width="25.375" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="9" style="26" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1">
+    <row r="1" spans="1:12" s="3" customFormat="1">
       <c r="A1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:12">
       <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>14</v>
@@ -1286,31 +1241,25 @@
         <v>18</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="H2" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="H2" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="K2" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="L2" s="26" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:12">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
         <v>125</v>
@@ -1328,225 +1277,192 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="I3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="B4" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" s="27" t="s">
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>134</v>
+      <c r="E4" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" t="s">
         <v>31</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="J4" s="23" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="7">
+      <c r="I4" s="7">
         <v>6</v>
       </c>
-      <c r="L4" s="7">
+      <c r="J4" s="7">
         <v>4</v>
       </c>
-      <c r="M4" s="27">
+      <c r="K4" s="26">
         <v>101</v>
       </c>
-      <c r="N4" s="23"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="B5" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="L4" s="23"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="B5" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="27" t="s">
-        <v>136</v>
+      <c r="E5" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
       </c>
-      <c r="G5" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" t="s">
         <v>33</v>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>1E-3</v>
       </c>
-      <c r="J5" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="K5" s="7">
+      <c r="I5" s="7">
         <v>6</v>
       </c>
-      <c r="L5" s="7">
+      <c r="J5" s="7">
         <v>4</v>
       </c>
-      <c r="M5" s="27">
+      <c r="K5" s="26">
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
-      <c r="B6" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="27" t="s">
+    <row r="6" spans="1:12">
+      <c r="B6" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>139</v>
+      <c r="E6" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="26" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>1E-3</v>
       </c>
-      <c r="J6" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="K6" s="7">
+      <c r="I6" s="7">
         <v>6</v>
       </c>
-      <c r="L6" s="7">
+      <c r="J6" s="7">
         <v>4</v>
       </c>
-      <c r="M6" s="27">
+      <c r="K6" s="26">
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="B7" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="27" t="s">
+    <row r="7" spans="1:12">
+      <c r="B7" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="27" t="s">
-        <v>142</v>
+      <c r="E7" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="G7" t="s">
         <v>37</v>
       </c>
-      <c r="I7">
+      <c r="H7">
         <v>0.02</v>
       </c>
-      <c r="J7" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="K7" s="7">
+      <c r="I7" s="7">
         <v>6</v>
       </c>
-      <c r="L7" s="7">
+      <c r="J7" s="7">
         <v>4</v>
       </c>
-      <c r="M7" s="27">
+      <c r="K7" s="26">
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="I11" s="23"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="I12" s="23"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="I13" s="23"/>
-      <c r="N13" s="23"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="I14" s="23"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="I15" s="23"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" spans="8:10">
-      <c r="H17" s="7"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="27"/>
-    </row>
-    <row r="18" spans="8:10">
-      <c r="H18" s="7"/>
-      <c r="I18" s="23"/>
-      <c r="J18" s="27"/>
-    </row>
-    <row r="19" spans="8:10">
-      <c r="H19" s="7"/>
-      <c r="I19" s="23"/>
-      <c r="J19" s="7"/>
-    </row>
-    <row r="20" spans="8:10">
-      <c r="I20" s="23"/>
-    </row>
-    <row r="21" spans="8:10">
-      <c r="I21" s="23"/>
-    </row>
-    <row r="22" spans="8:10">
-      <c r="I22" s="23"/>
+    <row r="11" spans="1:12">
+      <c r="H11" s="23"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" s="23"/>
+      <c r="L13" s="23"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="H16" s="23"/>
+    </row>
+    <row r="17" spans="7:8">
+      <c r="G17" s="7"/>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="7:8">
+      <c r="G18" s="7"/>
+      <c r="H18" s="23"/>
+    </row>
+    <row r="19" spans="7:8">
+      <c r="G19" s="7"/>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="7:8">
+      <c r="H20" s="23"/>
+    </row>
+    <row r="21" spans="7:8">
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="7:8">
+      <c r="H22" s="23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -1561,28 +1477,28 @@
   <sheetFormatPr defaultColWidth="22" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.5" style="27" customWidth="1"/>
-    <col min="6" max="6" width="18.75" style="27" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.375" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.75" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.5" style="26" customWidth="1"/>
+    <col min="6" max="6" width="18.75" style="26" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.375" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.75" style="26" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="35.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.25" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.375" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="22" style="27" customWidth="1"/>
-    <col min="19" max="16384" width="22" style="27"/>
+    <col min="12" max="12" width="10.25" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.375" style="26" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="22" style="26" customWidth="1"/>
+    <col min="19" max="16384" width="22" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="3" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="28" t="s">
         <v>39</v>
       </c>
       <c r="C1" s="10"/>
@@ -1617,10 +1533,10 @@
       <c r="H2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="I2" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="26" t="s">
         <v>45</v>
       </c>
       <c r="K2" s="7" t="s">
@@ -1662,16 +1578,16 @@
       <c r="F3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="27" t="s">
+      <c r="H3" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="26" t="s">
         <v>29</v>
       </c>
       <c r="K3" s="7" t="s">
@@ -1697,43 +1613,43 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <v>1</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>101</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="D4" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="7">
         <v>1</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="26">
         <v>1</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="L4" s="27">
+        <v>137</v>
+      </c>
+      <c r="L4" s="26">
         <v>0</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="26">
         <v>0</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="26">
         <v>5</v>
       </c>
-      <c r="O4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="P4" s="27">
+      <c r="O4" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="P4" s="26">
         <v>0</v>
       </c>
       <c r="Q4">
@@ -1741,105 +1657,105 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>2</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>101</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="26">
         <v>1</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="26">
         <v>2</v>
       </c>
       <c r="K5" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="26">
         <v>5</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="26">
         <v>2</v>
       </c>
-      <c r="N5" s="27">
+      <c r="N5" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>3</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>101</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="26">
         <v>1</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="26">
         <v>4</v>
       </c>
       <c r="K6" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="27">
+      <c r="L6" s="26">
         <v>10</v>
       </c>
-      <c r="M6" s="27">
+      <c r="M6" s="26">
         <v>3</v>
       </c>
-      <c r="N6" s="27">
+      <c r="N6" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>4</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>101</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="27" t="s">
-        <v>148</v>
-      </c>
-      <c r="F7" s="27" t="s">
+      <c r="E7" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="26">
         <v>2</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="26">
         <v>1</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="26">
         <v>1</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="26">
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1851,7 +1767,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="P7">
         <v>0.1</v>
@@ -1861,230 +1777,230 @@
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>5</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>101</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="26">
         <v>2</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>3</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="26">
         <v>5</v>
       </c>
       <c r="K8" t="s">
         <v>33</v>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="26">
         <v>0.05</v>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="26">
         <v>0.01</v>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>6</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>101</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="26">
         <v>2</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <v>4</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="26">
         <v>3</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="26">
         <v>5</v>
       </c>
       <c r="K9" t="s">
         <v>35</v>
       </c>
-      <c r="L9" s="27">
+      <c r="L9" s="26">
         <v>0.1</v>
       </c>
-      <c r="M9" s="27">
+      <c r="M9" s="26">
         <v>0.02</v>
       </c>
-      <c r="N9" s="27">
+      <c r="N9" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>7</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>101</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="26">
         <v>3</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="26">
         <v>1</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="26">
         <v>15</v>
       </c>
       <c r="K10" t="s">
         <v>37</v>
       </c>
-      <c r="L10" s="27">
+      <c r="L10" s="26">
         <v>0.2</v>
       </c>
-      <c r="M10" s="27">
+      <c r="M10" s="26">
         <v>0.1</v>
       </c>
-      <c r="N10" s="27">
+      <c r="N10" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>8</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>101</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="26">
         <v>3</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="26">
         <v>3</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="26">
         <v>5</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="26">
         <v>15</v>
       </c>
       <c r="K11" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="L11" s="27">
+      <c r="L11" s="26">
         <v>0.01</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="26">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="N11" s="27">
+      <c r="N11" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>9</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>101</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="26">
         <v>3</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="26">
         <v>4</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="26">
         <v>6</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="26">
         <v>15</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="L12" s="27">
+      <c r="L12" s="26">
         <v>0.05</v>
       </c>
-      <c r="M12" s="27">
+      <c r="M12" s="26">
         <v>0.01</v>
       </c>
-      <c r="N12" s="27">
+      <c r="N12" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>10</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>101</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="26">
         <v>4</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="26">
         <v>1</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="26">
         <v>7</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="26">
         <v>25</v>
       </c>
       <c r="K13" s="23" t="s">
@@ -2093,235 +2009,235 @@
       <c r="L13" s="7">
         <v>5</v>
       </c>
-      <c r="M13" s="27">
+      <c r="M13" s="26">
         <v>1</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>11</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>101</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="26">
         <v>4</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="26">
         <v>2</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="26">
         <v>25</v>
       </c>
       <c r="K14" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="L14" s="27">
+      <c r="L14" s="26">
         <v>50</v>
       </c>
-      <c r="M14" s="27">
+      <c r="M14" s="26">
         <v>20</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>12</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>101</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="26">
         <v>4</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="26">
         <v>3</v>
       </c>
-      <c r="J15" s="27">
+      <c r="J15" s="26">
         <v>25</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="L15" s="27">
+      <c r="L15" s="26">
         <v>5</v>
       </c>
-      <c r="M15" s="27">
+      <c r="M15" s="26">
         <v>5</v>
       </c>
-      <c r="N15" s="27">
+      <c r="N15" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>13</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>101</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="26">
         <v>5</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="26">
         <v>1</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="26">
         <v>10</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="26">
         <v>40</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="L16" s="27">
+      <c r="L16" s="26">
         <v>10</v>
       </c>
-      <c r="M16" s="27">
+      <c r="M16" s="26">
         <v>2</v>
       </c>
-      <c r="N16" s="27">
+      <c r="N16" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="2:14">
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>14</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>101</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="26">
         <v>5</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="26">
         <v>2</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="26">
         <v>11</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="26">
         <v>40</v>
       </c>
       <c r="K17" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="L17" s="27">
+      <c r="L17" s="26">
         <v>0.02</v>
       </c>
-      <c r="M17" s="27">
+      <c r="M17" s="26">
         <v>0.01</v>
       </c>
-      <c r="N17" s="27">
+      <c r="N17" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:14">
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>15</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>101</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="26">
         <v>5</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="26">
         <v>3</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="26">
         <v>12</v>
       </c>
-      <c r="J18" s="27">
+      <c r="J18" s="26">
         <v>40</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="L18" s="27">
+      <c r="L18" s="26">
         <v>5</v>
       </c>
-      <c r="M18" s="27">
+      <c r="M18" s="26">
         <v>1</v>
       </c>
-      <c r="N18" s="27">
+      <c r="N18" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="2:14">
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>16</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>101</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="26">
         <v>5</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="26">
         <v>4</v>
       </c>
-      <c r="J19" s="27">
+      <c r="J19" s="26">
         <v>40</v>
       </c>
       <c r="K19" s="23" t="s">
@@ -2330,92 +2246,92 @@
       <c r="L19" s="7">
         <v>0.02</v>
       </c>
-      <c r="M19" s="27">
+      <c r="M19" s="26">
         <v>0.01</v>
       </c>
-      <c r="N19" s="27">
+      <c r="N19" s="26">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:14">
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>17</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>101</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="26">
         <v>6</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="26">
         <v>2</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="26">
         <v>14</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="26">
         <v>55</v>
       </c>
       <c r="K20" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="L20" s="27">
+      <c r="L20" s="26">
         <v>0.02</v>
       </c>
-      <c r="M20" s="27">
+      <c r="M20" s="26">
         <v>0.01</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N20" s="26">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="2:14">
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <v>18</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>101</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="26" t="s">
         <v>101</v>
       </c>
       <c r="G21" s="7">
         <v>6</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="26">
         <v>3</v>
       </c>
-      <c r="I21" s="27">
+      <c r="I21" s="26">
         <v>15</v>
       </c>
-      <c r="J21" s="27">
+      <c r="J21" s="26">
         <v>55</v>
       </c>
       <c r="K21" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="L21" s="27">
+      <c r="L21" s="26">
         <v>0.2</v>
       </c>
-      <c r="M21" s="27">
+      <c r="M21" s="26">
         <v>0.1</v>
       </c>
-      <c r="N21" s="27">
+      <c r="N21" s="26">
         <v>3</v>
       </c>
     </row>
@@ -2455,19 +2371,19 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.625" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.75" style="27" customWidth="1"/>
-    <col min="8" max="8" width="9.375" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="27" customWidth="1"/>
-    <col min="11" max="11" width="17.375" style="27" customWidth="1"/>
-    <col min="12" max="12" width="16.75" style="27" customWidth="1"/>
-    <col min="13" max="13" width="21.25" style="27" customWidth="1"/>
-    <col min="14" max="16" width="9" style="27" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="27"/>
+    <col min="2" max="2" width="22.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.625" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="26" customWidth="1"/>
+    <col min="8" max="8" width="9.375" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="26" customWidth="1"/>
+    <col min="11" max="11" width="17.375" style="26" customWidth="1"/>
+    <col min="12" max="12" width="16.75" style="26" customWidth="1"/>
+    <col min="13" max="13" width="21.25" style="26" customWidth="1"/>
+    <col min="14" max="16" width="9" style="26" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="3" customFormat="1">
@@ -2518,7 +2434,7 @@
       <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>108</v>
       </c>
       <c r="F3" s="7" t="s">
@@ -2528,7 +2444,7 @@
       <c r="J3" s="7"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>110</v>
       </c>
       <c r="C4">
@@ -2537,7 +2453,7 @@
       <c r="D4" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="27" t="b">
+      <c r="E4" s="26" t="b">
         <v>0</v>
       </c>
       <c r="F4" s="23" t="s">
@@ -2545,7 +2461,7 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>112</v>
       </c>
       <c r="C5">
@@ -2554,7 +2470,7 @@
       <c r="D5" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="27" t="b">
+      <c r="E5" s="26" t="b">
         <v>0</v>
       </c>
       <c r="F5" s="23" t="s">
@@ -2562,7 +2478,7 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>114</v>
       </c>
       <c r="C6">
@@ -2571,7 +2487,7 @@
       <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="27" t="b">
+      <c r="E6" s="26" t="b">
         <v>1</v>
       </c>
       <c r="F6" s="23" t="s">
@@ -2579,50 +2495,50 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="I7" s="27"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="I8" s="27"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="I9" s="27"/>
+      <c r="I9" s="26"/>
       <c r="J9" s="25"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="I10" s="27"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="I11" s="27"/>
+      <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="I12" s="27"/>
+      <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="I13" s="27"/>
+      <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="I14" s="27"/>
+      <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:13">
-      <c r="I15" s="27"/>
+      <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="I16" s="27"/>
+      <c r="I16" s="26"/>
     </row>
     <row r="17" spans="5:9">
-      <c r="I17" s="27"/>
+      <c r="I17" s="26"/>
     </row>
     <row r="18" spans="5:9">
-      <c r="I18" s="27"/>
+      <c r="I18" s="26"/>
     </row>
     <row r="19" spans="5:9">
-      <c r="I19" s="27"/>
+      <c r="I19" s="26"/>
     </row>
     <row r="20" spans="5:9">
-      <c r="I20" s="27"/>
+      <c r="I20" s="26"/>
     </row>
     <row r="21" spans="5:9">
-      <c r="I21" s="27"/>
+      <c r="I21" s="26"/>
     </row>
     <row r="23" spans="5:9">
       <c r="E23" s="7"/>
@@ -2643,14 +2559,14 @@
       <c r="E32" s="7"/>
     </row>
     <row r="33" spans="5:9">
-      <c r="I33" s="27"/>
+      <c r="I33" s="26"/>
     </row>
     <row r="34" spans="5:9">
-      <c r="I34" s="27"/>
+      <c r="I34" s="26"/>
     </row>
     <row r="35" spans="5:9">
       <c r="E35" s="7"/>
-      <c r="I35" s="27"/>
+      <c r="I35" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -2664,20 +2580,20 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
-    <col min="2" max="2" width="16" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.625" style="27" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="27" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="27" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="27" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9" style="27" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="27"/>
+    <col min="2" max="2" width="16" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.625" style="26" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="26" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="26" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="26" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14" style="26" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="9" style="26" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="3" customFormat="1">
@@ -2713,10 +2629,10 @@
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <v>1</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="26">
         <v>0</v>
       </c>
       <c r="F4" s="1"/>
@@ -2726,10 +2642,10 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>2</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="26">
         <v>500</v>
       </c>
       <c r="F5" s="1"/>
@@ -2739,10 +2655,10 @@
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>3</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="26">
         <v>1500</v>
       </c>
       <c r="F6" s="1"/>
@@ -2752,2378 +2668,2378 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="B7" s="27">
+      <c r="B7" s="26">
         <v>4</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>2500</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>5</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>3250</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="B9" s="27">
+      <c r="B9" s="26">
         <v>6</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>4100</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>7</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>4950</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>8</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>5800</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>9</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="26">
         <v>6650</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>10</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="26">
         <v>7500</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>11</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="26">
         <v>8350</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>12</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="26">
         <v>9200</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>13</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="26">
         <v>10050</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>14</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="26">
         <v>10900</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>15</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="26">
         <v>11750</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>16</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="26">
         <v>12600</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>17</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="26">
         <v>13450</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <v>18</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="26">
         <v>14300</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>19</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="26">
         <v>15150</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>20</v>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="26">
         <v>16000</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>21</v>
       </c>
-      <c r="C24" s="27">
+      <c r="C24" s="26">
         <v>16850</v>
       </c>
     </row>
     <row r="25" spans="2:3">
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>22</v>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="26">
         <v>17700</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>23</v>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="26">
         <v>18550</v>
       </c>
     </row>
     <row r="27" spans="2:3">
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>24</v>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="26">
         <v>19400</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="B28" s="27">
+      <c r="B28" s="26">
         <v>25</v>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="26">
         <v>20250</v>
       </c>
     </row>
     <row r="29" spans="2:3">
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>26</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="26">
         <v>21100</v>
       </c>
     </row>
     <row r="30" spans="2:3">
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>27</v>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="26">
         <v>21950</v>
       </c>
     </row>
     <row r="31" spans="2:3">
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>28</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="26">
         <v>22800</v>
       </c>
     </row>
     <row r="32" spans="2:3">
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>29</v>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="26">
         <v>23650</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="B33" s="27">
+      <c r="B33" s="26">
         <v>30</v>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="26">
         <v>24500</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>31</v>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="26">
         <v>25350</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="B35" s="27">
+      <c r="B35" s="26">
         <v>32</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="26">
         <v>26200</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="27">
+      <c r="B36" s="26">
         <v>33</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="26">
         <v>27050</v>
       </c>
     </row>
     <row r="37" spans="2:3">
-      <c r="B37" s="27">
+      <c r="B37" s="26">
         <v>34</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="26">
         <v>27900</v>
       </c>
     </row>
     <row r="38" spans="2:3">
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <v>35</v>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="26">
         <v>28750</v>
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>36</v>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="26">
         <v>29600</v>
       </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>37</v>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="26">
         <v>30450</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="B41" s="27">
+      <c r="B41" s="26">
         <v>38</v>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="26">
         <v>31300</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="B42" s="27">
+      <c r="B42" s="26">
         <v>39</v>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="26">
         <v>32150</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="B43" s="27">
+      <c r="B43" s="26">
         <v>40</v>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="26">
         <v>33000</v>
       </c>
     </row>
     <row r="44" spans="2:3">
-      <c r="B44" s="27">
+      <c r="B44" s="26">
         <v>41</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="26">
         <v>33850</v>
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="B45" s="27">
+      <c r="B45" s="26">
         <v>42</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="26">
         <v>34700</v>
       </c>
     </row>
     <row r="46" spans="2:3">
-      <c r="B46" s="27">
+      <c r="B46" s="26">
         <v>43</v>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="26">
         <v>35550</v>
       </c>
     </row>
     <row r="47" spans="2:3">
-      <c r="B47" s="27">
+      <c r="B47" s="26">
         <v>44</v>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="26">
         <v>36400</v>
       </c>
     </row>
     <row r="48" spans="2:3">
-      <c r="B48" s="27">
+      <c r="B48" s="26">
         <v>45</v>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="26">
         <v>37250</v>
       </c>
     </row>
     <row r="49" spans="2:3">
-      <c r="B49" s="27">
+      <c r="B49" s="26">
         <v>46</v>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="26">
         <v>38100</v>
       </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="B50" s="27">
+      <c r="B50" s="26">
         <v>47</v>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="26">
         <v>38950</v>
       </c>
     </row>
     <row r="51" spans="2:3">
-      <c r="B51" s="27">
+      <c r="B51" s="26">
         <v>48</v>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="26">
         <v>39800</v>
       </c>
     </row>
     <row r="52" spans="2:3">
-      <c r="B52" s="27">
+      <c r="B52" s="26">
         <v>49</v>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="26">
         <v>40650</v>
       </c>
     </row>
     <row r="53" spans="2:3">
-      <c r="B53" s="27">
+      <c r="B53" s="26">
         <v>50</v>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="26">
         <v>41500</v>
       </c>
     </row>
     <row r="54" spans="2:3">
-      <c r="B54" s="27">
+      <c r="B54" s="26">
         <v>51</v>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="26">
         <v>42350</v>
       </c>
     </row>
     <row r="55" spans="2:3">
-      <c r="B55" s="27">
+      <c r="B55" s="26">
         <v>52</v>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="26">
         <v>43200</v>
       </c>
     </row>
     <row r="56" spans="2:3">
-      <c r="B56" s="27">
+      <c r="B56" s="26">
         <v>53</v>
       </c>
-      <c r="C56" s="27">
+      <c r="C56" s="26">
         <v>44050</v>
       </c>
     </row>
     <row r="57" spans="2:3">
-      <c r="B57" s="27">
+      <c r="B57" s="26">
         <v>54</v>
       </c>
-      <c r="C57" s="27">
+      <c r="C57" s="26">
         <v>44900</v>
       </c>
     </row>
     <row r="58" spans="2:3">
-      <c r="B58" s="27">
+      <c r="B58" s="26">
         <v>55</v>
       </c>
-      <c r="C58" s="27">
+      <c r="C58" s="26">
         <v>45750</v>
       </c>
     </row>
     <row r="59" spans="2:3">
-      <c r="B59" s="27">
+      <c r="B59" s="26">
         <v>56</v>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="26">
         <v>46600</v>
       </c>
     </row>
     <row r="60" spans="2:3">
-      <c r="B60" s="27">
+      <c r="B60" s="26">
         <v>57</v>
       </c>
-      <c r="C60" s="27">
+      <c r="C60" s="26">
         <v>47450</v>
       </c>
     </row>
     <row r="61" spans="2:3">
-      <c r="B61" s="27">
+      <c r="B61" s="26">
         <v>58</v>
       </c>
-      <c r="C61" s="27">
+      <c r="C61" s="26">
         <v>48300</v>
       </c>
     </row>
     <row r="62" spans="2:3">
-      <c r="B62" s="27">
+      <c r="B62" s="26">
         <v>59</v>
       </c>
-      <c r="C62" s="27">
+      <c r="C62" s="26">
         <v>49150</v>
       </c>
     </row>
     <row r="63" spans="2:3">
-      <c r="B63" s="27">
+      <c r="B63" s="26">
         <v>60</v>
       </c>
-      <c r="C63" s="27">
+      <c r="C63" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="64" spans="2:3">
-      <c r="B64" s="27">
+      <c r="B64" s="26">
         <v>61</v>
       </c>
-      <c r="C64" s="27">
+      <c r="C64" s="26">
         <v>50850</v>
       </c>
     </row>
     <row r="65" spans="2:3">
-      <c r="B65" s="27">
+      <c r="B65" s="26">
         <v>62</v>
       </c>
-      <c r="C65" s="27">
+      <c r="C65" s="26">
         <v>51700</v>
       </c>
     </row>
     <row r="66" spans="2:3">
-      <c r="B66" s="27">
+      <c r="B66" s="26">
         <v>63</v>
       </c>
-      <c r="C66" s="27">
+      <c r="C66" s="26">
         <v>52550</v>
       </c>
     </row>
     <row r="67" spans="2:3">
-      <c r="B67" s="27">
+      <c r="B67" s="26">
         <v>64</v>
       </c>
-      <c r="C67" s="27">
+      <c r="C67" s="26">
         <v>53400</v>
       </c>
     </row>
     <row r="68" spans="2:3">
-      <c r="B68" s="27">
+      <c r="B68" s="26">
         <v>65</v>
       </c>
-      <c r="C68" s="27">
+      <c r="C68" s="26">
         <v>54250</v>
       </c>
     </row>
     <row r="69" spans="2:3">
-      <c r="B69" s="27">
+      <c r="B69" s="26">
         <v>66</v>
       </c>
-      <c r="C69" s="27">
+      <c r="C69" s="26">
         <v>55100</v>
       </c>
     </row>
     <row r="70" spans="2:3">
-      <c r="B70" s="27">
+      <c r="B70" s="26">
         <v>67</v>
       </c>
-      <c r="C70" s="27">
+      <c r="C70" s="26">
         <v>55950</v>
       </c>
     </row>
     <row r="71" spans="2:3">
-      <c r="B71" s="27">
+      <c r="B71" s="26">
         <v>68</v>
       </c>
-      <c r="C71" s="27">
+      <c r="C71" s="26">
         <v>56800</v>
       </c>
     </row>
     <row r="72" spans="2:3">
-      <c r="B72" s="27">
+      <c r="B72" s="26">
         <v>69</v>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="26">
         <v>57650</v>
       </c>
     </row>
     <row r="73" spans="2:3">
-      <c r="B73" s="27">
+      <c r="B73" s="26">
         <v>70</v>
       </c>
-      <c r="C73" s="27">
+      <c r="C73" s="26">
         <v>58500</v>
       </c>
     </row>
     <row r="74" spans="2:3">
-      <c r="B74" s="27">
+      <c r="B74" s="26">
         <v>71</v>
       </c>
-      <c r="C74" s="27">
+      <c r="C74" s="26">
         <v>59350</v>
       </c>
     </row>
     <row r="75" spans="2:3">
-      <c r="B75" s="27">
+      <c r="B75" s="26">
         <v>72</v>
       </c>
-      <c r="C75" s="27">
+      <c r="C75" s="26">
         <v>60200</v>
       </c>
     </row>
     <row r="76" spans="2:3">
-      <c r="B76" s="27">
+      <c r="B76" s="26">
         <v>73</v>
       </c>
-      <c r="C76" s="27">
+      <c r="C76" s="26">
         <v>61050</v>
       </c>
     </row>
     <row r="77" spans="2:3">
-      <c r="B77" s="27">
+      <c r="B77" s="26">
         <v>74</v>
       </c>
-      <c r="C77" s="27">
+      <c r="C77" s="26">
         <v>61900</v>
       </c>
     </row>
     <row r="78" spans="2:3">
-      <c r="B78" s="27">
+      <c r="B78" s="26">
         <v>75</v>
       </c>
-      <c r="C78" s="27">
+      <c r="C78" s="26">
         <v>62750</v>
       </c>
     </row>
     <row r="79" spans="2:3">
-      <c r="B79" s="27">
+      <c r="B79" s="26">
         <v>76</v>
       </c>
-      <c r="C79" s="27">
+      <c r="C79" s="26">
         <v>63600</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="B80" s="27">
+      <c r="B80" s="26">
         <v>77</v>
       </c>
-      <c r="C80" s="27">
+      <c r="C80" s="26">
         <v>64450</v>
       </c>
     </row>
     <row r="81" spans="2:3">
-      <c r="B81" s="27">
+      <c r="B81" s="26">
         <v>78</v>
       </c>
-      <c r="C81" s="27">
+      <c r="C81" s="26">
         <v>65300</v>
       </c>
     </row>
     <row r="82" spans="2:3">
-      <c r="B82" s="27">
+      <c r="B82" s="26">
         <v>79</v>
       </c>
-      <c r="C82" s="27">
+      <c r="C82" s="26">
         <v>66150</v>
       </c>
     </row>
     <row r="83" spans="2:3">
-      <c r="B83" s="27">
+      <c r="B83" s="26">
         <v>80</v>
       </c>
-      <c r="C83" s="27">
+      <c r="C83" s="26">
         <v>67000</v>
       </c>
     </row>
     <row r="84" spans="2:3">
-      <c r="B84" s="27">
+      <c r="B84" s="26">
         <v>81</v>
       </c>
-      <c r="C84" s="27">
+      <c r="C84" s="26">
         <v>67850</v>
       </c>
     </row>
     <row r="85" spans="2:3">
-      <c r="B85" s="27">
+      <c r="B85" s="26">
         <v>82</v>
       </c>
-      <c r="C85" s="27">
+      <c r="C85" s="26">
         <v>68700</v>
       </c>
     </row>
     <row r="86" spans="2:3">
-      <c r="B86" s="27">
+      <c r="B86" s="26">
         <v>83</v>
       </c>
-      <c r="C86" s="27">
+      <c r="C86" s="26">
         <v>69550</v>
       </c>
     </row>
     <row r="87" spans="2:3">
-      <c r="B87" s="27">
+      <c r="B87" s="26">
         <v>84</v>
       </c>
-      <c r="C87" s="27">
+      <c r="C87" s="26">
         <v>70400</v>
       </c>
     </row>
     <row r="88" spans="2:3">
-      <c r="B88" s="27">
+      <c r="B88" s="26">
         <v>85</v>
       </c>
-      <c r="C88" s="27">
+      <c r="C88" s="26">
         <v>71250</v>
       </c>
     </row>
     <row r="89" spans="2:3">
-      <c r="B89" s="27">
+      <c r="B89" s="26">
         <v>86</v>
       </c>
-      <c r="C89" s="27">
+      <c r="C89" s="26">
         <v>72100</v>
       </c>
     </row>
     <row r="90" spans="2:3">
-      <c r="B90" s="27">
+      <c r="B90" s="26">
         <v>87</v>
       </c>
-      <c r="C90" s="27">
+      <c r="C90" s="26">
         <v>72950</v>
       </c>
     </row>
     <row r="91" spans="2:3">
-      <c r="B91" s="27">
+      <c r="B91" s="26">
         <v>88</v>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="26">
         <v>73800</v>
       </c>
     </row>
     <row r="92" spans="2:3">
-      <c r="B92" s="27">
+      <c r="B92" s="26">
         <v>89</v>
       </c>
-      <c r="C92" s="27">
+      <c r="C92" s="26">
         <v>74650</v>
       </c>
     </row>
     <row r="93" spans="2:3">
-      <c r="B93" s="27">
+      <c r="B93" s="26">
         <v>90</v>
       </c>
-      <c r="C93" s="27">
+      <c r="C93" s="26">
         <v>75500</v>
       </c>
     </row>
     <row r="94" spans="2:3">
-      <c r="B94" s="27">
+      <c r="B94" s="26">
         <v>91</v>
       </c>
-      <c r="C94" s="27">
+      <c r="C94" s="26">
         <v>76350</v>
       </c>
     </row>
     <row r="95" spans="2:3">
-      <c r="B95" s="27">
+      <c r="B95" s="26">
         <v>92</v>
       </c>
-      <c r="C95" s="27">
+      <c r="C95" s="26">
         <v>77200</v>
       </c>
     </row>
     <row r="96" spans="2:3">
-      <c r="B96" s="27">
+      <c r="B96" s="26">
         <v>93</v>
       </c>
-      <c r="C96" s="27">
+      <c r="C96" s="26">
         <v>78050</v>
       </c>
     </row>
     <row r="97" spans="2:3">
-      <c r="B97" s="27">
+      <c r="B97" s="26">
         <v>94</v>
       </c>
-      <c r="C97" s="27">
+      <c r="C97" s="26">
         <v>78900</v>
       </c>
     </row>
     <row r="98" spans="2:3">
-      <c r="B98" s="27">
+      <c r="B98" s="26">
         <v>95</v>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="26">
         <v>79750</v>
       </c>
     </row>
     <row r="99" spans="2:3">
-      <c r="B99" s="27">
+      <c r="B99" s="26">
         <v>96</v>
       </c>
-      <c r="C99" s="27">
+      <c r="C99" s="26">
         <v>80600</v>
       </c>
     </row>
     <row r="100" spans="2:3">
-      <c r="B100" s="27">
+      <c r="B100" s="26">
         <v>97</v>
       </c>
-      <c r="C100" s="27">
+      <c r="C100" s="26">
         <v>81450</v>
       </c>
     </row>
     <row r="101" spans="2:3">
-      <c r="B101" s="27">
+      <c r="B101" s="26">
         <v>98</v>
       </c>
-      <c r="C101" s="27">
+      <c r="C101" s="26">
         <v>82300</v>
       </c>
     </row>
     <row r="102" spans="2:3">
-      <c r="B102" s="27">
+      <c r="B102" s="26">
         <v>99</v>
       </c>
-      <c r="C102" s="27">
+      <c r="C102" s="26">
         <v>83150</v>
       </c>
     </row>
     <row r="103" spans="2:3">
-      <c r="B103" s="27">
+      <c r="B103" s="26">
         <v>100</v>
       </c>
-      <c r="C103" s="27">
+      <c r="C103" s="26">
         <v>84000</v>
       </c>
     </row>
     <row r="104" spans="2:3">
-      <c r="B104" s="27">
+      <c r="B104" s="26">
         <v>101</v>
       </c>
-      <c r="C104" s="27">
+      <c r="C104" s="26">
         <v>84850</v>
       </c>
     </row>
     <row r="105" spans="2:3">
-      <c r="B105" s="27">
+      <c r="B105" s="26">
         <v>102</v>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="26">
         <v>85700</v>
       </c>
     </row>
     <row r="106" spans="2:3">
-      <c r="B106" s="27">
+      <c r="B106" s="26">
         <v>103</v>
       </c>
-      <c r="C106" s="27">
+      <c r="C106" s="26">
         <v>86550</v>
       </c>
     </row>
     <row r="107" spans="2:3">
-      <c r="B107" s="27">
+      <c r="B107" s="26">
         <v>104</v>
       </c>
-      <c r="C107" s="27">
+      <c r="C107" s="26">
         <v>87400</v>
       </c>
     </row>
     <row r="108" spans="2:3">
-      <c r="B108" s="27">
+      <c r="B108" s="26">
         <v>105</v>
       </c>
-      <c r="C108" s="27">
+      <c r="C108" s="26">
         <v>88250</v>
       </c>
     </row>
     <row r="109" spans="2:3">
-      <c r="B109" s="27">
+      <c r="B109" s="26">
         <v>106</v>
       </c>
-      <c r="C109" s="27">
+      <c r="C109" s="26">
         <v>89100</v>
       </c>
     </row>
     <row r="110" spans="2:3">
-      <c r="B110" s="27">
+      <c r="B110" s="26">
         <v>107</v>
       </c>
-      <c r="C110" s="27">
+      <c r="C110" s="26">
         <v>89950</v>
       </c>
     </row>
     <row r="111" spans="2:3">
-      <c r="B111" s="27">
+      <c r="B111" s="26">
         <v>108</v>
       </c>
-      <c r="C111" s="27">
+      <c r="C111" s="26">
         <v>90800</v>
       </c>
     </row>
     <row r="112" spans="2:3">
-      <c r="B112" s="27">
+      <c r="B112" s="26">
         <v>109</v>
       </c>
-      <c r="C112" s="27">
+      <c r="C112" s="26">
         <v>91650</v>
       </c>
     </row>
     <row r="113" spans="2:3">
-      <c r="B113" s="27">
+      <c r="B113" s="26">
         <v>110</v>
       </c>
-      <c r="C113" s="27">
+      <c r="C113" s="26">
         <v>92500</v>
       </c>
     </row>
     <row r="114" spans="2:3">
-      <c r="B114" s="27">
+      <c r="B114" s="26">
         <v>111</v>
       </c>
-      <c r="C114" s="27">
+      <c r="C114" s="26">
         <v>93350</v>
       </c>
     </row>
     <row r="115" spans="2:3">
-      <c r="B115" s="27">
+      <c r="B115" s="26">
         <v>112</v>
       </c>
-      <c r="C115" s="27">
+      <c r="C115" s="26">
         <v>94200</v>
       </c>
     </row>
     <row r="116" spans="2:3">
-      <c r="B116" s="27">
+      <c r="B116" s="26">
         <v>113</v>
       </c>
-      <c r="C116" s="27">
+      <c r="C116" s="26">
         <v>95050</v>
       </c>
     </row>
     <row r="117" spans="2:3">
-      <c r="B117" s="27">
+      <c r="B117" s="26">
         <v>114</v>
       </c>
-      <c r="C117" s="27">
+      <c r="C117" s="26">
         <v>95900</v>
       </c>
     </row>
     <row r="118" spans="2:3">
-      <c r="B118" s="27">
+      <c r="B118" s="26">
         <v>115</v>
       </c>
-      <c r="C118" s="27">
+      <c r="C118" s="26">
         <v>96750</v>
       </c>
     </row>
     <row r="119" spans="2:3">
-      <c r="B119" s="27">
+      <c r="B119" s="26">
         <v>116</v>
       </c>
-      <c r="C119" s="27">
+      <c r="C119" s="26">
         <v>97600</v>
       </c>
     </row>
     <row r="120" spans="2:3">
-      <c r="B120" s="27">
+      <c r="B120" s="26">
         <v>117</v>
       </c>
-      <c r="C120" s="27">
+      <c r="C120" s="26">
         <v>98450</v>
       </c>
     </row>
     <row r="121" spans="2:3">
-      <c r="B121" s="27">
+      <c r="B121" s="26">
         <v>118</v>
       </c>
-      <c r="C121" s="27">
+      <c r="C121" s="26">
         <v>99300</v>
       </c>
     </row>
     <row r="122" spans="2:3">
-      <c r="B122" s="27">
+      <c r="B122" s="26">
         <v>119</v>
       </c>
-      <c r="C122" s="27">
+      <c r="C122" s="26">
         <v>100150</v>
       </c>
     </row>
     <row r="123" spans="2:3">
-      <c r="B123" s="27">
+      <c r="B123" s="26">
         <v>120</v>
       </c>
-      <c r="C123" s="27">
+      <c r="C123" s="26">
         <v>101000</v>
       </c>
     </row>
     <row r="124" spans="2:3">
-      <c r="B124" s="27">
+      <c r="B124" s="26">
         <v>121</v>
       </c>
-      <c r="C124" s="27">
+      <c r="C124" s="26">
         <v>101850</v>
       </c>
     </row>
     <row r="125" spans="2:3">
-      <c r="B125" s="27">
+      <c r="B125" s="26">
         <v>122</v>
       </c>
-      <c r="C125" s="27">
+      <c r="C125" s="26">
         <v>102700</v>
       </c>
     </row>
     <row r="126" spans="2:3">
-      <c r="B126" s="27">
+      <c r="B126" s="26">
         <v>123</v>
       </c>
-      <c r="C126" s="27">
+      <c r="C126" s="26">
         <v>103550</v>
       </c>
     </row>
     <row r="127" spans="2:3">
-      <c r="B127" s="27">
+      <c r="B127" s="26">
         <v>124</v>
       </c>
-      <c r="C127" s="27">
+      <c r="C127" s="26">
         <v>104400</v>
       </c>
     </row>
     <row r="128" spans="2:3">
-      <c r="B128" s="27">
+      <c r="B128" s="26">
         <v>125</v>
       </c>
-      <c r="C128" s="27">
+      <c r="C128" s="26">
         <v>105250</v>
       </c>
     </row>
     <row r="129" spans="2:3">
-      <c r="B129" s="27">
+      <c r="B129" s="26">
         <v>126</v>
       </c>
-      <c r="C129" s="27">
+      <c r="C129" s="26">
         <v>106100</v>
       </c>
     </row>
     <row r="130" spans="2:3">
-      <c r="B130" s="27">
+      <c r="B130" s="26">
         <v>127</v>
       </c>
-      <c r="C130" s="27">
+      <c r="C130" s="26">
         <v>106950</v>
       </c>
     </row>
     <row r="131" spans="2:3">
-      <c r="B131" s="27">
+      <c r="B131" s="26">
         <v>128</v>
       </c>
-      <c r="C131" s="27">
+      <c r="C131" s="26">
         <v>107800</v>
       </c>
     </row>
     <row r="132" spans="2:3">
-      <c r="B132" s="27">
+      <c r="B132" s="26">
         <v>129</v>
       </c>
-      <c r="C132" s="27">
+      <c r="C132" s="26">
         <v>108650</v>
       </c>
     </row>
     <row r="133" spans="2:3">
-      <c r="B133" s="27">
+      <c r="B133" s="26">
         <v>130</v>
       </c>
-      <c r="C133" s="27">
+      <c r="C133" s="26">
         <v>109500</v>
       </c>
     </row>
     <row r="134" spans="2:3">
-      <c r="B134" s="27">
+      <c r="B134" s="26">
         <v>131</v>
       </c>
-      <c r="C134" s="27">
+      <c r="C134" s="26">
         <v>110350</v>
       </c>
     </row>
     <row r="135" spans="2:3">
-      <c r="B135" s="27">
+      <c r="B135" s="26">
         <v>132</v>
       </c>
-      <c r="C135" s="27">
+      <c r="C135" s="26">
         <v>111200</v>
       </c>
     </row>
     <row r="136" spans="2:3">
-      <c r="B136" s="27">
+      <c r="B136" s="26">
         <v>133</v>
       </c>
-      <c r="C136" s="27">
+      <c r="C136" s="26">
         <v>112050</v>
       </c>
     </row>
     <row r="137" spans="2:3">
-      <c r="B137" s="27">
+      <c r="B137" s="26">
         <v>134</v>
       </c>
-      <c r="C137" s="27">
+      <c r="C137" s="26">
         <v>112900</v>
       </c>
     </row>
     <row r="138" spans="2:3">
-      <c r="B138" s="27">
+      <c r="B138" s="26">
         <v>135</v>
       </c>
-      <c r="C138" s="27">
+      <c r="C138" s="26">
         <v>113750</v>
       </c>
     </row>
     <row r="139" spans="2:3">
-      <c r="B139" s="27">
+      <c r="B139" s="26">
         <v>136</v>
       </c>
-      <c r="C139" s="27">
+      <c r="C139" s="26">
         <v>114600</v>
       </c>
     </row>
     <row r="140" spans="2:3">
-      <c r="B140" s="27">
+      <c r="B140" s="26">
         <v>137</v>
       </c>
-      <c r="C140" s="27">
+      <c r="C140" s="26">
         <v>115450</v>
       </c>
     </row>
     <row r="141" spans="2:3">
-      <c r="B141" s="27">
+      <c r="B141" s="26">
         <v>138</v>
       </c>
-      <c r="C141" s="27">
+      <c r="C141" s="26">
         <v>116300</v>
       </c>
     </row>
     <row r="142" spans="2:3">
-      <c r="B142" s="27">
+      <c r="B142" s="26">
         <v>139</v>
       </c>
-      <c r="C142" s="27">
+      <c r="C142" s="26">
         <v>117150</v>
       </c>
     </row>
     <row r="143" spans="2:3">
-      <c r="B143" s="27">
+      <c r="B143" s="26">
         <v>140</v>
       </c>
-      <c r="C143" s="27">
+      <c r="C143" s="26">
         <v>118000</v>
       </c>
     </row>
     <row r="144" spans="2:3">
-      <c r="B144" s="27">
+      <c r="B144" s="26">
         <v>141</v>
       </c>
-      <c r="C144" s="27">
+      <c r="C144" s="26">
         <v>118850</v>
       </c>
     </row>
     <row r="145" spans="2:3">
-      <c r="B145" s="27">
+      <c r="B145" s="26">
         <v>142</v>
       </c>
-      <c r="C145" s="27">
+      <c r="C145" s="26">
         <v>119700</v>
       </c>
     </row>
     <row r="146" spans="2:3">
-      <c r="B146" s="27">
+      <c r="B146" s="26">
         <v>143</v>
       </c>
-      <c r="C146" s="27">
+      <c r="C146" s="26">
         <v>120550</v>
       </c>
     </row>
     <row r="147" spans="2:3">
-      <c r="B147" s="27">
+      <c r="B147" s="26">
         <v>144</v>
       </c>
-      <c r="C147" s="27">
+      <c r="C147" s="26">
         <v>121400</v>
       </c>
     </row>
     <row r="148" spans="2:3">
-      <c r="B148" s="27">
+      <c r="B148" s="26">
         <v>145</v>
       </c>
-      <c r="C148" s="27">
+      <c r="C148" s="26">
         <v>122250</v>
       </c>
     </row>
     <row r="149" spans="2:3">
-      <c r="B149" s="27">
+      <c r="B149" s="26">
         <v>146</v>
       </c>
-      <c r="C149" s="27">
+      <c r="C149" s="26">
         <v>123100</v>
       </c>
     </row>
     <row r="150" spans="2:3">
-      <c r="B150" s="27">
+      <c r="B150" s="26">
         <v>147</v>
       </c>
-      <c r="C150" s="27">
+      <c r="C150" s="26">
         <v>123950</v>
       </c>
     </row>
     <row r="151" spans="2:3">
-      <c r="B151" s="27">
+      <c r="B151" s="26">
         <v>148</v>
       </c>
-      <c r="C151" s="27">
+      <c r="C151" s="26">
         <v>124800</v>
       </c>
     </row>
     <row r="152" spans="2:3">
-      <c r="B152" s="27">
+      <c r="B152" s="26">
         <v>149</v>
       </c>
-      <c r="C152" s="27">
+      <c r="C152" s="26">
         <v>125650</v>
       </c>
     </row>
     <row r="153" spans="2:3">
-      <c r="B153" s="27">
+      <c r="B153" s="26">
         <v>150</v>
       </c>
-      <c r="C153" s="27">
+      <c r="C153" s="26">
         <v>126500</v>
       </c>
     </row>
     <row r="154" spans="2:3">
-      <c r="B154" s="27">
+      <c r="B154" s="26">
         <v>151</v>
       </c>
-      <c r="C154" s="27">
+      <c r="C154" s="26">
         <v>127350</v>
       </c>
     </row>
     <row r="155" spans="2:3">
-      <c r="B155" s="27">
+      <c r="B155" s="26">
         <v>152</v>
       </c>
-      <c r="C155" s="27">
+      <c r="C155" s="26">
         <v>128200</v>
       </c>
     </row>
     <row r="156" spans="2:3">
-      <c r="B156" s="27">
+      <c r="B156" s="26">
         <v>153</v>
       </c>
-      <c r="C156" s="27">
+      <c r="C156" s="26">
         <v>129050</v>
       </c>
     </row>
     <row r="157" spans="2:3">
-      <c r="B157" s="27">
+      <c r="B157" s="26">
         <v>154</v>
       </c>
-      <c r="C157" s="27">
+      <c r="C157" s="26">
         <v>129900</v>
       </c>
     </row>
     <row r="158" spans="2:3">
-      <c r="B158" s="27">
+      <c r="B158" s="26">
         <v>155</v>
       </c>
-      <c r="C158" s="27">
+      <c r="C158" s="26">
         <v>130750</v>
       </c>
     </row>
     <row r="159" spans="2:3">
-      <c r="B159" s="27">
+      <c r="B159" s="26">
         <v>156</v>
       </c>
-      <c r="C159" s="27">
+      <c r="C159" s="26">
         <v>131600</v>
       </c>
     </row>
     <row r="160" spans="2:3">
-      <c r="B160" s="27">
+      <c r="B160" s="26">
         <v>157</v>
       </c>
-      <c r="C160" s="27">
+      <c r="C160" s="26">
         <v>132450</v>
       </c>
     </row>
     <row r="161" spans="2:3">
-      <c r="B161" s="27">
+      <c r="B161" s="26">
         <v>158</v>
       </c>
-      <c r="C161" s="27">
+      <c r="C161" s="26">
         <v>133300</v>
       </c>
     </row>
     <row r="162" spans="2:3">
-      <c r="B162" s="27">
+      <c r="B162" s="26">
         <v>159</v>
       </c>
-      <c r="C162" s="27">
+      <c r="C162" s="26">
         <v>134150</v>
       </c>
     </row>
     <row r="163" spans="2:3">
-      <c r="B163" s="27">
+      <c r="B163" s="26">
         <v>160</v>
       </c>
-      <c r="C163" s="27">
+      <c r="C163" s="26">
         <v>135000</v>
       </c>
     </row>
     <row r="164" spans="2:3">
-      <c r="B164" s="27">
+      <c r="B164" s="26">
         <v>161</v>
       </c>
-      <c r="C164" s="27">
+      <c r="C164" s="26">
         <v>135850</v>
       </c>
     </row>
     <row r="165" spans="2:3">
-      <c r="B165" s="27">
+      <c r="B165" s="26">
         <v>162</v>
       </c>
-      <c r="C165" s="27">
+      <c r="C165" s="26">
         <v>136700</v>
       </c>
     </row>
     <row r="166" spans="2:3">
-      <c r="B166" s="27">
+      <c r="B166" s="26">
         <v>163</v>
       </c>
-      <c r="C166" s="27">
+      <c r="C166" s="26">
         <v>137550</v>
       </c>
     </row>
     <row r="167" spans="2:3">
-      <c r="B167" s="27">
+      <c r="B167" s="26">
         <v>164</v>
       </c>
-      <c r="C167" s="27">
+      <c r="C167" s="26">
         <v>138400</v>
       </c>
     </row>
     <row r="168" spans="2:3">
-      <c r="B168" s="27">
+      <c r="B168" s="26">
         <v>165</v>
       </c>
-      <c r="C168" s="27">
+      <c r="C168" s="26">
         <v>139250</v>
       </c>
     </row>
     <row r="169" spans="2:3">
-      <c r="B169" s="27">
+      <c r="B169" s="26">
         <v>166</v>
       </c>
-      <c r="C169" s="27">
+      <c r="C169" s="26">
         <v>140100</v>
       </c>
     </row>
     <row r="170" spans="2:3">
-      <c r="B170" s="27">
+      <c r="B170" s="26">
         <v>167</v>
       </c>
-      <c r="C170" s="27">
+      <c r="C170" s="26">
         <v>140950</v>
       </c>
     </row>
     <row r="171" spans="2:3">
-      <c r="B171" s="27">
+      <c r="B171" s="26">
         <v>168</v>
       </c>
-      <c r="C171" s="27">
+      <c r="C171" s="26">
         <v>141800</v>
       </c>
     </row>
     <row r="172" spans="2:3">
-      <c r="B172" s="27">
+      <c r="B172" s="26">
         <v>169</v>
       </c>
-      <c r="C172" s="27">
+      <c r="C172" s="26">
         <v>142650</v>
       </c>
     </row>
     <row r="173" spans="2:3">
-      <c r="B173" s="27">
+      <c r="B173" s="26">
         <v>170</v>
       </c>
-      <c r="C173" s="27">
+      <c r="C173" s="26">
         <v>143500</v>
       </c>
     </row>
     <row r="174" spans="2:3">
-      <c r="B174" s="27">
+      <c r="B174" s="26">
         <v>171</v>
       </c>
-      <c r="C174" s="27">
+      <c r="C174" s="26">
         <v>144350</v>
       </c>
     </row>
     <row r="175" spans="2:3">
-      <c r="B175" s="27">
+      <c r="B175" s="26">
         <v>172</v>
       </c>
-      <c r="C175" s="27">
+      <c r="C175" s="26">
         <v>145200</v>
       </c>
     </row>
     <row r="176" spans="2:3">
-      <c r="B176" s="27">
+      <c r="B176" s="26">
         <v>173</v>
       </c>
-      <c r="C176" s="27">
+      <c r="C176" s="26">
         <v>146050</v>
       </c>
     </row>
     <row r="177" spans="2:3">
-      <c r="B177" s="27">
+      <c r="B177" s="26">
         <v>174</v>
       </c>
-      <c r="C177" s="27">
+      <c r="C177" s="26">
         <v>146900</v>
       </c>
     </row>
     <row r="178" spans="2:3">
-      <c r="B178" s="27">
+      <c r="B178" s="26">
         <v>175</v>
       </c>
-      <c r="C178" s="27">
+      <c r="C178" s="26">
         <v>147750</v>
       </c>
     </row>
     <row r="179" spans="2:3">
-      <c r="B179" s="27">
+      <c r="B179" s="26">
         <v>176</v>
       </c>
-      <c r="C179" s="27">
+      <c r="C179" s="26">
         <v>148600</v>
       </c>
     </row>
     <row r="180" spans="2:3">
-      <c r="B180" s="27">
+      <c r="B180" s="26">
         <v>177</v>
       </c>
-      <c r="C180" s="27">
+      <c r="C180" s="26">
         <v>149450</v>
       </c>
     </row>
     <row r="181" spans="2:3">
-      <c r="B181" s="27">
+      <c r="B181" s="26">
         <v>178</v>
       </c>
-      <c r="C181" s="27">
+      <c r="C181" s="26">
         <v>150300</v>
       </c>
     </row>
     <row r="182" spans="2:3">
-      <c r="B182" s="27">
+      <c r="B182" s="26">
         <v>179</v>
       </c>
-      <c r="C182" s="27">
+      <c r="C182" s="26">
         <v>151150</v>
       </c>
     </row>
     <row r="183" spans="2:3">
-      <c r="B183" s="27">
+      <c r="B183" s="26">
         <v>180</v>
       </c>
-      <c r="C183" s="27">
+      <c r="C183" s="26">
         <v>152000</v>
       </c>
     </row>
     <row r="184" spans="2:3">
-      <c r="B184" s="27">
+      <c r="B184" s="26">
         <v>181</v>
       </c>
-      <c r="C184" s="27">
+      <c r="C184" s="26">
         <v>152850</v>
       </c>
     </row>
     <row r="185" spans="2:3">
-      <c r="B185" s="27">
+      <c r="B185" s="26">
         <v>182</v>
       </c>
-      <c r="C185" s="27">
+      <c r="C185" s="26">
         <v>153700</v>
       </c>
     </row>
     <row r="186" spans="2:3">
-      <c r="B186" s="27">
+      <c r="B186" s="26">
         <v>183</v>
       </c>
-      <c r="C186" s="27">
+      <c r="C186" s="26">
         <v>154550</v>
       </c>
     </row>
     <row r="187" spans="2:3">
-      <c r="B187" s="27">
+      <c r="B187" s="26">
         <v>184</v>
       </c>
-      <c r="C187" s="27">
+      <c r="C187" s="26">
         <v>155400</v>
       </c>
     </row>
     <row r="188" spans="2:3">
-      <c r="B188" s="27">
+      <c r="B188" s="26">
         <v>185</v>
       </c>
-      <c r="C188" s="27">
+      <c r="C188" s="26">
         <v>156250</v>
       </c>
     </row>
     <row r="189" spans="2:3">
-      <c r="B189" s="27">
+      <c r="B189" s="26">
         <v>186</v>
       </c>
-      <c r="C189" s="27">
+      <c r="C189" s="26">
         <v>157100</v>
       </c>
     </row>
     <row r="190" spans="2:3">
-      <c r="B190" s="27">
+      <c r="B190" s="26">
         <v>187</v>
       </c>
-      <c r="C190" s="27">
+      <c r="C190" s="26">
         <v>157950</v>
       </c>
     </row>
     <row r="191" spans="2:3">
-      <c r="B191" s="27">
+      <c r="B191" s="26">
         <v>188</v>
       </c>
-      <c r="C191" s="27">
+      <c r="C191" s="26">
         <v>158800</v>
       </c>
     </row>
     <row r="192" spans="2:3">
-      <c r="B192" s="27">
+      <c r="B192" s="26">
         <v>189</v>
       </c>
-      <c r="C192" s="27">
+      <c r="C192" s="26">
         <v>159650</v>
       </c>
     </row>
     <row r="193" spans="2:3">
-      <c r="B193" s="27">
+      <c r="B193" s="26">
         <v>190</v>
       </c>
-      <c r="C193" s="27">
+      <c r="C193" s="26">
         <v>160500</v>
       </c>
     </row>
     <row r="194" spans="2:3">
-      <c r="B194" s="27">
+      <c r="B194" s="26">
         <v>191</v>
       </c>
-      <c r="C194" s="27">
+      <c r="C194" s="26">
         <v>161350</v>
       </c>
     </row>
     <row r="195" spans="2:3">
-      <c r="B195" s="27">
+      <c r="B195" s="26">
         <v>192</v>
       </c>
-      <c r="C195" s="27">
+      <c r="C195" s="26">
         <v>162200</v>
       </c>
     </row>
     <row r="196" spans="2:3">
-      <c r="B196" s="27">
+      <c r="B196" s="26">
         <v>193</v>
       </c>
-      <c r="C196" s="27">
+      <c r="C196" s="26">
         <v>163050</v>
       </c>
     </row>
     <row r="197" spans="2:3">
-      <c r="B197" s="27">
+      <c r="B197" s="26">
         <v>194</v>
       </c>
-      <c r="C197" s="27">
+      <c r="C197" s="26">
         <v>163900</v>
       </c>
     </row>
     <row r="198" spans="2:3">
-      <c r="B198" s="27">
+      <c r="B198" s="26">
         <v>195</v>
       </c>
-      <c r="C198" s="27">
+      <c r="C198" s="26">
         <v>164750</v>
       </c>
     </row>
     <row r="199" spans="2:3">
-      <c r="B199" s="27">
+      <c r="B199" s="26">
         <v>196</v>
       </c>
-      <c r="C199" s="27">
+      <c r="C199" s="26">
         <v>165600</v>
       </c>
     </row>
     <row r="200" spans="2:3">
-      <c r="B200" s="27">
+      <c r="B200" s="26">
         <v>197</v>
       </c>
-      <c r="C200" s="27">
+      <c r="C200" s="26">
         <v>166450</v>
       </c>
     </row>
     <row r="201" spans="2:3">
-      <c r="B201" s="27">
+      <c r="B201" s="26">
         <v>198</v>
       </c>
-      <c r="C201" s="27">
+      <c r="C201" s="26">
         <v>167300</v>
       </c>
     </row>
     <row r="202" spans="2:3">
-      <c r="B202" s="27">
+      <c r="B202" s="26">
         <v>199</v>
       </c>
-      <c r="C202" s="27">
+      <c r="C202" s="26">
         <v>168150</v>
       </c>
     </row>
     <row r="203" spans="2:3">
-      <c r="B203" s="27">
+      <c r="B203" s="26">
         <v>200</v>
       </c>
-      <c r="C203" s="27">
+      <c r="C203" s="26">
         <v>169000</v>
       </c>
     </row>
     <row r="204" spans="2:3">
-      <c r="B204" s="27">
+      <c r="B204" s="26">
         <v>201</v>
       </c>
-      <c r="C204" s="27">
+      <c r="C204" s="26">
         <v>169850</v>
       </c>
     </row>
     <row r="205" spans="2:3">
-      <c r="B205" s="27">
+      <c r="B205" s="26">
         <v>202</v>
       </c>
-      <c r="C205" s="27">
+      <c r="C205" s="26">
         <v>170700</v>
       </c>
     </row>
     <row r="206" spans="2:3">
-      <c r="B206" s="27">
+      <c r="B206" s="26">
         <v>203</v>
       </c>
-      <c r="C206" s="27">
+      <c r="C206" s="26">
         <v>171550</v>
       </c>
     </row>
     <row r="207" spans="2:3">
-      <c r="B207" s="27">
+      <c r="B207" s="26">
         <v>204</v>
       </c>
-      <c r="C207" s="27">
+      <c r="C207" s="26">
         <v>172400</v>
       </c>
     </row>
     <row r="208" spans="2:3">
-      <c r="B208" s="27">
+      <c r="B208" s="26">
         <v>205</v>
       </c>
-      <c r="C208" s="27">
+      <c r="C208" s="26">
         <v>173250</v>
       </c>
     </row>
     <row r="209" spans="2:3">
-      <c r="B209" s="27">
+      <c r="B209" s="26">
         <v>206</v>
       </c>
-      <c r="C209" s="27">
+      <c r="C209" s="26">
         <v>174100</v>
       </c>
     </row>
     <row r="210" spans="2:3">
-      <c r="B210" s="27">
+      <c r="B210" s="26">
         <v>207</v>
       </c>
-      <c r="C210" s="27">
+      <c r="C210" s="26">
         <v>174950</v>
       </c>
     </row>
     <row r="211" spans="2:3">
-      <c r="B211" s="27">
+      <c r="B211" s="26">
         <v>208</v>
       </c>
-      <c r="C211" s="27">
+      <c r="C211" s="26">
         <v>175800</v>
       </c>
     </row>
     <row r="212" spans="2:3">
-      <c r="B212" s="27">
+      <c r="B212" s="26">
         <v>209</v>
       </c>
-      <c r="C212" s="27">
+      <c r="C212" s="26">
         <v>176650</v>
       </c>
     </row>
     <row r="213" spans="2:3">
-      <c r="B213" s="27">
+      <c r="B213" s="26">
         <v>210</v>
       </c>
-      <c r="C213" s="27">
+      <c r="C213" s="26">
         <v>177500</v>
       </c>
     </row>
     <row r="214" spans="2:3">
-      <c r="B214" s="27">
+      <c r="B214" s="26">
         <v>211</v>
       </c>
-      <c r="C214" s="27">
+      <c r="C214" s="26">
         <v>178350</v>
       </c>
     </row>
     <row r="215" spans="2:3">
-      <c r="B215" s="27">
+      <c r="B215" s="26">
         <v>212</v>
       </c>
-      <c r="C215" s="27">
+      <c r="C215" s="26">
         <v>179200</v>
       </c>
     </row>
     <row r="216" spans="2:3">
-      <c r="B216" s="27">
+      <c r="B216" s="26">
         <v>213</v>
       </c>
-      <c r="C216" s="27">
+      <c r="C216" s="26">
         <v>180050</v>
       </c>
     </row>
     <row r="217" spans="2:3">
-      <c r="B217" s="27">
+      <c r="B217" s="26">
         <v>214</v>
       </c>
-      <c r="C217" s="27">
+      <c r="C217" s="26">
         <v>180900</v>
       </c>
     </row>
     <row r="218" spans="2:3">
-      <c r="B218" s="27">
+      <c r="B218" s="26">
         <v>215</v>
       </c>
-      <c r="C218" s="27">
+      <c r="C218" s="26">
         <v>181750</v>
       </c>
     </row>
     <row r="219" spans="2:3">
-      <c r="B219" s="27">
+      <c r="B219" s="26">
         <v>216</v>
       </c>
-      <c r="C219" s="27">
+      <c r="C219" s="26">
         <v>182600</v>
       </c>
     </row>
     <row r="220" spans="2:3">
-      <c r="B220" s="27">
+      <c r="B220" s="26">
         <v>217</v>
       </c>
-      <c r="C220" s="27">
+      <c r="C220" s="26">
         <v>183450</v>
       </c>
     </row>
     <row r="221" spans="2:3">
-      <c r="B221" s="27">
+      <c r="B221" s="26">
         <v>218</v>
       </c>
-      <c r="C221" s="27">
+      <c r="C221" s="26">
         <v>184300</v>
       </c>
     </row>
     <row r="222" spans="2:3">
-      <c r="B222" s="27">
+      <c r="B222" s="26">
         <v>219</v>
       </c>
-      <c r="C222" s="27">
+      <c r="C222" s="26">
         <v>185150</v>
       </c>
     </row>
     <row r="223" spans="2:3">
-      <c r="B223" s="27">
+      <c r="B223" s="26">
         <v>220</v>
       </c>
-      <c r="C223" s="27">
+      <c r="C223" s="26">
         <v>186000</v>
       </c>
     </row>
     <row r="224" spans="2:3">
-      <c r="B224" s="27">
+      <c r="B224" s="26">
         <v>221</v>
       </c>
-      <c r="C224" s="27">
+      <c r="C224" s="26">
         <v>186850</v>
       </c>
     </row>
     <row r="225" spans="2:3">
-      <c r="B225" s="27">
+      <c r="B225" s="26">
         <v>222</v>
       </c>
-      <c r="C225" s="27">
+      <c r="C225" s="26">
         <v>187700</v>
       </c>
     </row>
     <row r="226" spans="2:3">
-      <c r="B226" s="27">
+      <c r="B226" s="26">
         <v>223</v>
       </c>
-      <c r="C226" s="27">
+      <c r="C226" s="26">
         <v>188550</v>
       </c>
     </row>
     <row r="227" spans="2:3">
-      <c r="B227" s="27">
+      <c r="B227" s="26">
         <v>224</v>
       </c>
-      <c r="C227" s="27">
+      <c r="C227" s="26">
         <v>189400</v>
       </c>
     </row>
     <row r="228" spans="2:3">
-      <c r="B228" s="27">
+      <c r="B228" s="26">
         <v>225</v>
       </c>
-      <c r="C228" s="27">
+      <c r="C228" s="26">
         <v>190250</v>
       </c>
     </row>
     <row r="229" spans="2:3">
-      <c r="B229" s="27">
+      <c r="B229" s="26">
         <v>226</v>
       </c>
-      <c r="C229" s="27">
+      <c r="C229" s="26">
         <v>191100</v>
       </c>
     </row>
     <row r="230" spans="2:3">
-      <c r="B230" s="27">
+      <c r="B230" s="26">
         <v>227</v>
       </c>
-      <c r="C230" s="27">
+      <c r="C230" s="26">
         <v>191950</v>
       </c>
     </row>
     <row r="231" spans="2:3">
-      <c r="B231" s="27">
+      <c r="B231" s="26">
         <v>228</v>
       </c>
-      <c r="C231" s="27">
+      <c r="C231" s="26">
         <v>192800</v>
       </c>
     </row>
     <row r="232" spans="2:3">
-      <c r="B232" s="27">
+      <c r="B232" s="26">
         <v>229</v>
       </c>
-      <c r="C232" s="27">
+      <c r="C232" s="26">
         <v>193650</v>
       </c>
     </row>
     <row r="233" spans="2:3">
-      <c r="B233" s="27">
+      <c r="B233" s="26">
         <v>230</v>
       </c>
-      <c r="C233" s="27">
+      <c r="C233" s="26">
         <v>194500</v>
       </c>
     </row>
     <row r="234" spans="2:3">
-      <c r="B234" s="27">
+      <c r="B234" s="26">
         <v>231</v>
       </c>
-      <c r="C234" s="27">
+      <c r="C234" s="26">
         <v>195350</v>
       </c>
     </row>
     <row r="235" spans="2:3">
-      <c r="B235" s="27">
+      <c r="B235" s="26">
         <v>232</v>
       </c>
-      <c r="C235" s="27">
+      <c r="C235" s="26">
         <v>196200</v>
       </c>
     </row>
     <row r="236" spans="2:3">
-      <c r="B236" s="27">
+      <c r="B236" s="26">
         <v>233</v>
       </c>
-      <c r="C236" s="27">
+      <c r="C236" s="26">
         <v>197050</v>
       </c>
     </row>
     <row r="237" spans="2:3">
-      <c r="B237" s="27">
+      <c r="B237" s="26">
         <v>234</v>
       </c>
-      <c r="C237" s="27">
+      <c r="C237" s="26">
         <v>197900</v>
       </c>
     </row>
     <row r="238" spans="2:3">
-      <c r="B238" s="27">
+      <c r="B238" s="26">
         <v>235</v>
       </c>
-      <c r="C238" s="27">
+      <c r="C238" s="26">
         <v>198750</v>
       </c>
     </row>
     <row r="239" spans="2:3">
-      <c r="B239" s="27">
+      <c r="B239" s="26">
         <v>236</v>
       </c>
-      <c r="C239" s="27">
+      <c r="C239" s="26">
         <v>199600</v>
       </c>
     </row>
     <row r="240" spans="2:3">
-      <c r="B240" s="27">
+      <c r="B240" s="26">
         <v>237</v>
       </c>
-      <c r="C240" s="27">
+      <c r="C240" s="26">
         <v>200450</v>
       </c>
     </row>
     <row r="241" spans="2:3">
-      <c r="B241" s="27">
+      <c r="B241" s="26">
         <v>238</v>
       </c>
-      <c r="C241" s="27">
+      <c r="C241" s="26">
         <v>201300</v>
       </c>
     </row>
     <row r="242" spans="2:3">
-      <c r="B242" s="27">
+      <c r="B242" s="26">
         <v>239</v>
       </c>
-      <c r="C242" s="27">
+      <c r="C242" s="26">
         <v>202150</v>
       </c>
     </row>
     <row r="243" spans="2:3">
-      <c r="B243" s="27">
+      <c r="B243" s="26">
         <v>240</v>
       </c>
-      <c r="C243" s="27">
+      <c r="C243" s="26">
         <v>203000</v>
       </c>
     </row>
     <row r="244" spans="2:3">
-      <c r="B244" s="27">
+      <c r="B244" s="26">
         <v>241</v>
       </c>
-      <c r="C244" s="27">
+      <c r="C244" s="26">
         <v>203850</v>
       </c>
     </row>
     <row r="245" spans="2:3">
-      <c r="B245" s="27">
+      <c r="B245" s="26">
         <v>242</v>
       </c>
-      <c r="C245" s="27">
+      <c r="C245" s="26">
         <v>204700</v>
       </c>
     </row>
     <row r="246" spans="2:3">
-      <c r="B246" s="27">
+      <c r="B246" s="26">
         <v>243</v>
       </c>
-      <c r="C246" s="27">
+      <c r="C246" s="26">
         <v>205550</v>
       </c>
     </row>
     <row r="247" spans="2:3">
-      <c r="B247" s="27">
+      <c r="B247" s="26">
         <v>244</v>
       </c>
-      <c r="C247" s="27">
+      <c r="C247" s="26">
         <v>206400</v>
       </c>
     </row>
     <row r="248" spans="2:3">
-      <c r="B248" s="27">
+      <c r="B248" s="26">
         <v>245</v>
       </c>
-      <c r="C248" s="27">
+      <c r="C248" s="26">
         <v>207250</v>
       </c>
     </row>
     <row r="249" spans="2:3">
-      <c r="B249" s="27">
+      <c r="B249" s="26">
         <v>246</v>
       </c>
-      <c r="C249" s="27">
+      <c r="C249" s="26">
         <v>208100</v>
       </c>
     </row>
     <row r="250" spans="2:3">
-      <c r="B250" s="27">
+      <c r="B250" s="26">
         <v>247</v>
       </c>
-      <c r="C250" s="27">
+      <c r="C250" s="26">
         <v>208950</v>
       </c>
     </row>
     <row r="251" spans="2:3">
-      <c r="B251" s="27">
+      <c r="B251" s="26">
         <v>248</v>
       </c>
-      <c r="C251" s="27">
+      <c r="C251" s="26">
         <v>209800</v>
       </c>
     </row>
     <row r="252" spans="2:3">
-      <c r="B252" s="27">
+      <c r="B252" s="26">
         <v>249</v>
       </c>
-      <c r="C252" s="27">
+      <c r="C252" s="26">
         <v>210650</v>
       </c>
     </row>
     <row r="253" spans="2:3">
-      <c r="B253" s="27">
+      <c r="B253" s="26">
         <v>250</v>
       </c>
-      <c r="C253" s="27">
+      <c r="C253" s="26">
         <v>211500</v>
       </c>
     </row>
     <row r="254" spans="2:3">
-      <c r="B254" s="27">
+      <c r="B254" s="26">
         <v>251</v>
       </c>
-      <c r="C254" s="27">
+      <c r="C254" s="26">
         <v>212350</v>
       </c>
     </row>
     <row r="255" spans="2:3">
-      <c r="B255" s="27">
+      <c r="B255" s="26">
         <v>252</v>
       </c>
-      <c r="C255" s="27">
+      <c r="C255" s="26">
         <v>213200</v>
       </c>
     </row>
     <row r="256" spans="2:3">
-      <c r="B256" s="27">
+      <c r="B256" s="26">
         <v>253</v>
       </c>
-      <c r="C256" s="27">
+      <c r="C256" s="26">
         <v>214050</v>
       </c>
     </row>
     <row r="257" spans="2:3">
-      <c r="B257" s="27">
+      <c r="B257" s="26">
         <v>254</v>
       </c>
-      <c r="C257" s="27">
+      <c r="C257" s="26">
         <v>214900</v>
       </c>
     </row>
     <row r="258" spans="2:3">
-      <c r="B258" s="27">
+      <c r="B258" s="26">
         <v>255</v>
       </c>
-      <c r="C258" s="27">
+      <c r="C258" s="26">
         <v>215750</v>
       </c>
     </row>
     <row r="259" spans="2:3">
-      <c r="B259" s="27">
+      <c r="B259" s="26">
         <v>256</v>
       </c>
-      <c r="C259" s="27">
+      <c r="C259" s="26">
         <v>216600</v>
       </c>
     </row>
     <row r="260" spans="2:3">
-      <c r="B260" s="27">
+      <c r="B260" s="26">
         <v>257</v>
       </c>
-      <c r="C260" s="27">
+      <c r="C260" s="26">
         <v>217450</v>
       </c>
     </row>
     <row r="261" spans="2:3">
-      <c r="B261" s="27">
+      <c r="B261" s="26">
         <v>258</v>
       </c>
-      <c r="C261" s="27">
+      <c r="C261" s="26">
         <v>218300</v>
       </c>
     </row>
     <row r="262" spans="2:3">
-      <c r="B262" s="27">
+      <c r="B262" s="26">
         <v>259</v>
       </c>
-      <c r="C262" s="27">
+      <c r="C262" s="26">
         <v>219150</v>
       </c>
     </row>
     <row r="263" spans="2:3">
-      <c r="B263" s="27">
+      <c r="B263" s="26">
         <v>260</v>
       </c>
-      <c r="C263" s="27">
+      <c r="C263" s="26">
         <v>220000</v>
       </c>
     </row>
     <row r="264" spans="2:3">
-      <c r="B264" s="27">
+      <c r="B264" s="26">
         <v>261</v>
       </c>
-      <c r="C264" s="27">
+      <c r="C264" s="26">
         <v>220850</v>
       </c>
     </row>
     <row r="265" spans="2:3">
-      <c r="B265" s="27">
+      <c r="B265" s="26">
         <v>262</v>
       </c>
-      <c r="C265" s="27">
+      <c r="C265" s="26">
         <v>221700</v>
       </c>
     </row>
     <row r="266" spans="2:3">
-      <c r="B266" s="27">
+      <c r="B266" s="26">
         <v>263</v>
       </c>
-      <c r="C266" s="27">
+      <c r="C266" s="26">
         <v>222550</v>
       </c>
     </row>
     <row r="267" spans="2:3">
-      <c r="B267" s="27">
+      <c r="B267" s="26">
         <v>264</v>
       </c>
-      <c r="C267" s="27">
+      <c r="C267" s="26">
         <v>223400</v>
       </c>
     </row>
     <row r="268" spans="2:3">
-      <c r="B268" s="27">
+      <c r="B268" s="26">
         <v>265</v>
       </c>
-      <c r="C268" s="27">
+      <c r="C268" s="26">
         <v>224250</v>
       </c>
     </row>
     <row r="269" spans="2:3">
-      <c r="B269" s="27">
+      <c r="B269" s="26">
         <v>266</v>
       </c>
-      <c r="C269" s="27">
+      <c r="C269" s="26">
         <v>225100</v>
       </c>
     </row>
     <row r="270" spans="2:3">
-      <c r="B270" s="27">
+      <c r="B270" s="26">
         <v>267</v>
       </c>
-      <c r="C270" s="27">
+      <c r="C270" s="26">
         <v>225950</v>
       </c>
     </row>
     <row r="271" spans="2:3">
-      <c r="B271" s="27">
+      <c r="B271" s="26">
         <v>268</v>
       </c>
-      <c r="C271" s="27">
+      <c r="C271" s="26">
         <v>226800</v>
       </c>
     </row>
     <row r="272" spans="2:3">
-      <c r="B272" s="27">
+      <c r="B272" s="26">
         <v>269</v>
       </c>
-      <c r="C272" s="27">
+      <c r="C272" s="26">
         <v>227650</v>
       </c>
     </row>
     <row r="273" spans="2:3">
-      <c r="B273" s="27">
+      <c r="B273" s="26">
         <v>270</v>
       </c>
-      <c r="C273" s="27">
+      <c r="C273" s="26">
         <v>228500</v>
       </c>
     </row>
     <row r="274" spans="2:3">
-      <c r="B274" s="27">
+      <c r="B274" s="26">
         <v>271</v>
       </c>
-      <c r="C274" s="27">
+      <c r="C274" s="26">
         <v>229350</v>
       </c>
     </row>
     <row r="275" spans="2:3">
-      <c r="B275" s="27">
+      <c r="B275" s="26">
         <v>272</v>
       </c>
-      <c r="C275" s="27">
+      <c r="C275" s="26">
         <v>230200</v>
       </c>
     </row>
     <row r="276" spans="2:3">
-      <c r="B276" s="27">
+      <c r="B276" s="26">
         <v>273</v>
       </c>
-      <c r="C276" s="27">
+      <c r="C276" s="26">
         <v>231050</v>
       </c>
     </row>
     <row r="277" spans="2:3">
-      <c r="B277" s="27">
+      <c r="B277" s="26">
         <v>274</v>
       </c>
-      <c r="C277" s="27">
+      <c r="C277" s="26">
         <v>231900</v>
       </c>
     </row>
     <row r="278" spans="2:3">
-      <c r="B278" s="27">
+      <c r="B278" s="26">
         <v>275</v>
       </c>
-      <c r="C278" s="27">
+      <c r="C278" s="26">
         <v>232750</v>
       </c>
     </row>
     <row r="279" spans="2:3">
-      <c r="B279" s="27">
+      <c r="B279" s="26">
         <v>276</v>
       </c>
-      <c r="C279" s="27">
+      <c r="C279" s="26">
         <v>233600</v>
       </c>
     </row>
     <row r="280" spans="2:3">
-      <c r="B280" s="27">
+      <c r="B280" s="26">
         <v>277</v>
       </c>
-      <c r="C280" s="27">
+      <c r="C280" s="26">
         <v>234450</v>
       </c>
     </row>
     <row r="281" spans="2:3">
-      <c r="B281" s="27">
+      <c r="B281" s="26">
         <v>278</v>
       </c>
-      <c r="C281" s="27">
+      <c r="C281" s="26">
         <v>235300</v>
       </c>
     </row>
     <row r="282" spans="2:3">
-      <c r="B282" s="27">
+      <c r="B282" s="26">
         <v>279</v>
       </c>
-      <c r="C282" s="27">
+      <c r="C282" s="26">
         <v>236150</v>
       </c>
     </row>
     <row r="283" spans="2:3">
-      <c r="B283" s="27">
+      <c r="B283" s="26">
         <v>280</v>
       </c>
-      <c r="C283" s="27">
+      <c r="C283" s="26">
         <v>237000</v>
       </c>
     </row>
     <row r="284" spans="2:3">
-      <c r="B284" s="27">
+      <c r="B284" s="26">
         <v>281</v>
       </c>
-      <c r="C284" s="27">
+      <c r="C284" s="26">
         <v>237850</v>
       </c>
     </row>
     <row r="285" spans="2:3">
-      <c r="B285" s="27">
+      <c r="B285" s="26">
         <v>282</v>
       </c>
-      <c r="C285" s="27">
+      <c r="C285" s="26">
         <v>238700</v>
       </c>
     </row>
     <row r="286" spans="2:3">
-      <c r="B286" s="27">
+      <c r="B286" s="26">
         <v>283</v>
       </c>
-      <c r="C286" s="27">
+      <c r="C286" s="26">
         <v>239550</v>
       </c>
     </row>
     <row r="287" spans="2:3">
-      <c r="B287" s="27">
+      <c r="B287" s="26">
         <v>284</v>
       </c>
-      <c r="C287" s="27">
+      <c r="C287" s="26">
         <v>240400</v>
       </c>
     </row>
     <row r="288" spans="2:3">
-      <c r="B288" s="27">
+      <c r="B288" s="26">
         <v>285</v>
       </c>
-      <c r="C288" s="27">
+      <c r="C288" s="26">
         <v>241250</v>
       </c>
     </row>
     <row r="289" spans="2:3">
-      <c r="B289" s="27">
+      <c r="B289" s="26">
         <v>286</v>
       </c>
-      <c r="C289" s="27">
+      <c r="C289" s="26">
         <v>242100</v>
       </c>
     </row>
     <row r="290" spans="2:3">
-      <c r="B290" s="27">
+      <c r="B290" s="26">
         <v>287</v>
       </c>
-      <c r="C290" s="27">
+      <c r="C290" s="26">
         <v>242950</v>
       </c>
     </row>
     <row r="291" spans="2:3">
-      <c r="B291" s="27">
+      <c r="B291" s="26">
         <v>288</v>
       </c>
-      <c r="C291" s="27">
+      <c r="C291" s="26">
         <v>243800</v>
       </c>
     </row>
     <row r="292" spans="2:3">
-      <c r="B292" s="27">
+      <c r="B292" s="26">
         <v>289</v>
       </c>
-      <c r="C292" s="27">
+      <c r="C292" s="26">
         <v>244650</v>
       </c>
     </row>
     <row r="293" spans="2:3">
-      <c r="B293" s="27">
+      <c r="B293" s="26">
         <v>290</v>
       </c>
-      <c r="C293" s="27">
+      <c r="C293" s="26">
         <v>245500</v>
       </c>
     </row>
     <row r="294" spans="2:3">
-      <c r="B294" s="27">
+      <c r="B294" s="26">
         <v>291</v>
       </c>
-      <c r="C294" s="27">
+      <c r="C294" s="26">
         <v>246350</v>
       </c>
     </row>
     <row r="295" spans="2:3">
-      <c r="B295" s="27">
+      <c r="B295" s="26">
         <v>292</v>
       </c>
-      <c r="C295" s="27">
+      <c r="C295" s="26">
         <v>247200</v>
       </c>
     </row>
     <row r="296" spans="2:3">
-      <c r="B296" s="27">
+      <c r="B296" s="26">
         <v>293</v>
       </c>
-      <c r="C296" s="27">
+      <c r="C296" s="26">
         <v>248050</v>
       </c>
     </row>
     <row r="297" spans="2:3">
-      <c r="B297" s="27">
+      <c r="B297" s="26">
         <v>294</v>
       </c>
-      <c r="C297" s="27">
+      <c r="C297" s="26">
         <v>248900</v>
       </c>
     </row>
     <row r="298" spans="2:3">
-      <c r="B298" s="27">
+      <c r="B298" s="26">
         <v>295</v>
       </c>
-      <c r="C298" s="27">
+      <c r="C298" s="26">
         <v>249750</v>
       </c>
     </row>
     <row r="299" spans="2:3">
-      <c r="B299" s="27">
+      <c r="B299" s="26">
         <v>296</v>
       </c>
-      <c r="C299" s="27">
+      <c r="C299" s="26">
         <v>250600</v>
       </c>
     </row>
     <row r="300" spans="2:3">
-      <c r="B300" s="27">
+      <c r="B300" s="26">
         <v>297</v>
       </c>
-      <c r="C300" s="27">
+      <c r="C300" s="26">
         <v>251450</v>
       </c>
     </row>
     <row r="301" spans="2:3">
-      <c r="B301" s="27">
+      <c r="B301" s="26">
         <v>298</v>
       </c>
-      <c r="C301" s="27">
+      <c r="C301" s="26">
         <v>252300</v>
       </c>
     </row>
     <row r="302" spans="2:3">
-      <c r="B302" s="27">
+      <c r="B302" s="26">
         <v>299</v>
       </c>
-      <c r="C302" s="27">
+      <c r="C302" s="26">
         <v>253150</v>
       </c>
     </row>
     <row r="303" spans="2:3">
-      <c r="B303" s="27">
+      <c r="B303" s="26">
         <v>300</v>
       </c>
-      <c r="C303" s="27">
+      <c r="C303" s="26">
         <v>254000</v>
       </c>
     </row>
@@ -5140,18 +5056,18 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.75" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.75" style="26" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="9" style="27" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="27"/>
+    <col min="5" max="7" width="9" style="26" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>118</v>
       </c>
     </row>
@@ -5163,7 +5079,7 @@
       <c r="C2" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="26" t="s">
         <v>19</v>
       </c>
     </row>
@@ -5180,7 +5096,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -5191,7 +5107,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="B5" s="27">
+      <c r="B5" s="26">
         <v>2</v>
       </c>
       <c r="C5" t="s">

--- a/Shared/XLS/Mastery.xlsx
+++ b/Shared/XLS/Mastery.xlsx
@@ -393,14 +393,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>도</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>권총</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>소총</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -429,14 +421,6 @@
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
   <si>
-    <t>Mastery_Pistol</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>Pistol</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
     <t>Mastery_Rifle</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
@@ -470,6 +454,22 @@
   </si>
   <si>
     <t>OPT_ATKSPEED_GreatSword_Buff</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mastery_Shuriken</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리검</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shuriken</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>태도</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1076,7 +1076,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1262,7 +1262,7 @@
     <row r="3" spans="1:12">
       <c r="A3" s="4"/>
       <c r="B3" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>24</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>25</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>121</v>
@@ -1306,7 +1306,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -1330,16 +1330,16 @@
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="D5" s="26" t="s">
         <v>32</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F5" t="s">
         <v>2</v>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="D6" s="26" t="s">
         <v>34</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F6" s="22" t="s">
         <v>4</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="7" spans="1:12">
       <c r="B7" s="26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>36</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F7" s="22" t="s">
         <v>4</v>
@@ -1620,10 +1620,10 @@
         <v>101</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F4" s="26" t="s">
         <v>53</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="L4" s="26">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>5</v>
       </c>
       <c r="O4" s="26" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="P4" s="26">
         <v>0</v>
@@ -1737,7 +1737,7 @@
         <v>62</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F7" s="26" t="s">
         <v>63</v>
@@ -1755,7 +1755,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -1767,7 +1767,7 @@
         <v>5</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="P7">
         <v>0.1</v>
